--- a/workspaces/btc_daily_14days/drawdown/drawdown_30.xlsx
+++ b/workspaces/btc_daily_14days/drawdown/drawdown_30.xlsx
@@ -575,46 +575,46 @@
         <v>20</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.485504077856717</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.106036697464155</v>
+        <v>-4.092714761686061</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-4.502021908328629</v>
+        <v>-4.488103662688097</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-4.372741136479299</v>
+        <v>-4.35924874278129</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-14.92258977685566</v>
+        <v>-14.87533134933216</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-14.62865272370206</v>
+        <v>-14.58173328182963</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-14.71702083816628</v>
+        <v>-14.67004677602565</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-25.20606055473508</v>
+        <v>-25.12520676843878</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-20.26363662686676</v>
+        <v>-20.19845326168493</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-11.09822837301279</v>
+        <v>-11.06272479346087</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-16.31840894201473</v>
+        <v>-16.26640030233061</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-16.28774071876987</v>
+        <v>-16.23606976056917</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-16.71355453663727</v>
+        <v>-16.66016701745638</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-21.48311838120389</v>
+        <v>-21.41455241742233</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>12</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-10.8267716535471</v>
+        <v>-10.79199924285736</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-20.77683178419054</v>
+        <v>-20.70984038769073</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-37.85185751349411</v>
+        <v>-37.73067450098972</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-29.39131636183835</v>
+        <v>-29.2973313249044</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-38.27912910897785</v>
+        <v>-38.15645118540326</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-37.99099970136237</v>
+        <v>-37.86864478423616</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-29.73946979132478</v>
+        <v>-29.6438563306694</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-30.21507099616097</v>
+        <v>-30.11748353292784</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-30.28376629772021</v>
+        <v>-30.18587221740607</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-31.14301077104248</v>
+        <v>-31.04282150544751</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-23.00191081168566</v>
+        <v>-22.92801640808788</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-22.97292843225532</v>
+        <v>-22.89936896418241</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-23.40044355957252</v>
+        <v>-23.32514848776493</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-23.15570143208136</v>
+        <v>-23.08121908409127</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>5</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-12.49343832020088</v>
+        <v>-12.45315791702808</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-34.1134871317393</v>
+        <v>-34.00330955032978</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-34.5169520765395</v>
+        <v>-34.40598773750219</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-34.39512238228047</v>
+        <v>-34.28464459012132</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-34.94265194770293</v>
+        <v>-34.83019146496105</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-34.65373508612399</v>
+        <v>-34.54160150195318</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-34.74709065822756</v>
+        <v>-34.63496531929925</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-35.22396869090898</v>
+        <v>-35.10985693741731</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-35.29393840847901</v>
+        <v>-35.17951464819148</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-36.15446393338614</v>
+        <v>-36.03773121106867</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-36.36856085173262</v>
+        <v>-36.25135472941024</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-16.28832747062742</v>
+        <v>-16.23596307841407</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-16.71421411142409</v>
+        <v>-16.66011205289441</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-16.46783306065754</v>
+        <v>-16.4145524174246</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>12</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>14.17322834645668</v>
+        <v>14.12763585318109</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>29.23553370281892</v>
+        <v>29.1417737682414</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>28.84776353944019</v>
+        <v>28.75474304124089</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>20.645753570806</v>
+        <v>20.57910223293135</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>11.77024538029863</v>
+        <v>11.73245621373411</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>20.4144226720405</v>
+        <v>20.34934608498591</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>11.9889571288463</v>
+        <v>11.95075670692206</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>11.52365822070833</v>
+        <v>11.48741523355539</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>11.46527645137349</v>
+        <v>11.4293093977546</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>10.61633859040414</v>
+        <v>10.58265285243102</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>10.4138395723886</v>
+        <v>10.38059181001709</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-6.261138133058708</v>
+        <v>-6.240906594338348</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.673675112829798</v>
+        <v>1.668674956197123</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>10.28492944657697</v>
+        <v>10.25211424924206</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>10</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>17.50656167978548</v>
+        <v>17.44993749499997</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5.896432658519821</v>
+        <v>5.877652966533503</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.502891289486683</v>
+        <v>5.484873749308356</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.63463265041635</v>
+        <v>5.616171967566586</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5.097000665542453</v>
+        <v>5.080590155267537</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-4.61658115256111</v>
+        <v>-4.601047795656505</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-4.702531894870866</v>
+        <v>-4.686950543212355</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.845466796657831</v>
+        <v>4.830626930381925</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>14.80537956910425</v>
+        <v>14.75841161582807</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-6.087606614988616</v>
+        <v>-6.06744557480949</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>13.75562787897339</v>
+        <v>13.71138865137341</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>13.79365811996368</v>
+        <v>13.74913045056647</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>13.37530597755768</v>
+        <v>13.33242793969612</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>13.62926010084993</v>
+        <v>13.5854475825754</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>27</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>17.87693205016208</v>
+        <v>17.81857692608172</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5.155519707589612</v>
+        <v>5.138978748014843</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4.761804954736853</v>
+        <v>4.74603377561877</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4.893374337254691</v>
+        <v>4.877156468231711</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8.062982354483431</v>
+        <v>8.036760984779946</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.654234476069355</v>
+        <v>4.639721272615581</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>11.98915582510325</v>
+        <v>11.95052489461056</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>4.103499072376458</v>
+        <v>4.090937889804685</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>7.754480365367755</v>
+        <v>7.73003843298077</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.5196273669404334</v>
+        <v>-0.5174116603556627</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>6.701234926848969</v>
+        <v>6.679558388867001</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.023589549642679</v>
+        <v>3.013722042477923</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.11232160341924</v>
+        <v>-1.108417910038895</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.8619691424377436</v>
+        <v>-0.858996861867368</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>34</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>6.330091091556064</v>
+        <v>6.308762058910567</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.777779603548446</v>
+        <v>1.772077861458499</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>10.21121906273567</v>
+        <v>10.17730629056045</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.457371697890757</v>
+        <v>4.442335926971026</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.9753338184956846</v>
+        <v>0.9719876199428938</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>7.162936281348856</v>
+        <v>7.139959604201501</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-7.648181099995909</v>
+        <v>-7.622908823498641</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>6.613489029536922</v>
+        <v>6.592490226558539</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.287371134447689</v>
+        <v>-2.279207429741668</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.1921088859852773</v>
+        <v>-0.1909347615512615</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.345678398117649</v>
+        <v>-3.334690053731975</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.3625989205365627</v>
+        <v>-0.3614966115870857</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5.11565538225679</v>
+        <v>5.099163528517437</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.416727743178747</v>
+        <v>2.408976994340108</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>32</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.6315616797886037</v>
+        <v>0.6287433873880843</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2.145527705521097</v>
+        <v>2.138512402477552</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>8.004300160448622</v>
+        <v>7.977124959022944</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>8.136712135251976</v>
+        <v>8.109240351455192</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4.47156031174103</v>
+        <v>4.456580951313072</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>11.02830173914273</v>
+        <v>10.99213957762433</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>17.20578292834981</v>
+        <v>17.14918216304492</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>13.6114504919115</v>
+        <v>13.56692662015546</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>10.4222663347845</v>
+        <v>10.38848238727937</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>12.70509017056172</v>
+        <v>12.66357807606526</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>12.50337249735738</v>
+        <v>12.46206526586037</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>9.407406390632531</v>
+        <v>9.376176219536234</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>12.12262253615928</v>
+        <v>12.08265155981076</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>15.51168942956497</v>
+        <v>15.46044758257256</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>49</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.5677861695859434</v>
+        <v>0.5651228423506467</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.9972836280271764</v>
+        <v>0.9939719446538007</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.644479718557662</v>
+        <v>2.634708817990209</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>8.90274345888762</v>
+        <v>8.872129136608429</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>12.45182882824182</v>
+        <v>12.40977780959849</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>6.622400016308795</v>
+        <v>6.600255803542503</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>8.583290764715905</v>
+        <v>8.554419619253743</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>10.16184549461811</v>
+        <v>10.12795830879519</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>10.10316468953997</v>
+        <v>10.06974489515192</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>5.162671558695855</v>
+        <v>5.145582719885155</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>4.959067014307365</v>
+        <v>4.942193645469736</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>4.994928999701195</v>
+        <v>4.977841867611133</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>4.574520476112205</v>
+        <v>4.559024010392761</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>4.826420932771001</v>
+        <v>4.809937378495619</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>10.00656167979002</v>
+        <v>10.1917153246551</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>10.48105942684388</v>
+        <v>10.67056582698759</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>8.004460333113798</v>
+        <v>8.154685703226434</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>8.137016367141911</v>
+        <v>8.290296672893582</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>11.77117344429774</v>
+        <v>11.98842366272062</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>12.07190874736818</v>
+        <v>12.29129750721756</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>14.0769306799972</v>
+        <v>14.3338390287829</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>13.6124936099093</v>
+        <v>13.85985519531976</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>17.73016513815782</v>
+        <v>18.0504667500716</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>14.79445414665592</v>
+        <v>15.06184447988231</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>20.85976639049697</v>
+        <v>21.23929703767094</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>14.6318238043057</v>
+        <v>14.8992972287739</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>20.48358503845657</v>
+        <v>20.85575047203864</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>15.64041736515614</v>
+        <v>15.92587311448932</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>56</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-7.850581177352829</v>
+        <v>-7.82677316483403</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3.038686173427017</v>
+        <v>3.028594608503475</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>9.791241415367082</v>
+        <v>9.758794798826969</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>17.07287603900459</v>
+        <v>17.01714756861785</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>14.75086897060436</v>
+        <v>14.70268732065543</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>7.900150506563477</v>
+        <v>7.874333007963543</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.6633565368859635</v>
+        <v>0.6602481738151269</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.1954335517809014</v>
+        <v>0.1940371028464014</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.713370179731847</v>
+        <v>3.700886372856949</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>6.442155897715651</v>
+        <v>6.421082738382722</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.8678148119889499</v>
+        <v>0.8637828537089121</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>11.64810618940653</v>
+        <v>11.60994349374776</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>9.438329516157417</v>
+        <v>9.40715482172849</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>9.688803160905735</v>
+        <v>9.656876154003967</v>
       </c>
     </row>
     <row r="17">
@@ -1144,49 +1144,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.352715525943871</v>
+        <v>1.399247103701015</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-7.95326176038585</v>
+        <v>-8.178363471999042</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-5.271651710277368</v>
+        <v>-5.408061856540733</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-6.682152340978348</v>
+        <v>-6.855151662379015</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.60249168874892</v>
+        <v>-2.659822106498979</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.7755098039918238</v>
+        <v>0.8077547105337501</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.8500306043294756</v>
+        <v>-0.8651368393642187</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.76435602746421</v>
+        <v>1.822703264577541</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.379764244191428</v>
+        <v>-1.411906819760553</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.774433595084489</v>
+        <v>-3.875588648167678</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.64755020973017</v>
+        <v>0.678433055631217</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.0008248624856150855</v>
+        <v>0.01447220745571798</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>5.078650117437455</v>
+        <v>5.240488155060298</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>6.864257414404442</v>
+        <v>7.077511074638885</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>79</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>3.202764211435593</v>
+        <v>3.193161654819285</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.3254699341261329</v>
+        <v>0.3244487294789948</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.06927488110103752</v>
+        <v>-0.07040494027187805</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-7.539917844103641</v>
+        <v>-7.520806594384666</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.056892313821592</v>
+        <v>2.049603014818111</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>4.89029418262276</v>
+        <v>4.875834020488327</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>6.074724762864662</v>
+        <v>6.057105439914181</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>6.876607517412175</v>
+        <v>6.856871856998815</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>4.280134832902903</v>
+        <v>4.267650165923889</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>11.04289262020463</v>
+        <v>11.01185484570267</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>8.302643638838603</v>
+        <v>8.278559729215033</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>12.14536189992413</v>
+        <v>12.11041124099056</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>11.72413591187601</v>
+        <v>11.69015663004594</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>10.70528395825473</v>
+        <v>10.67405517751212</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.055236073018968</v>
+        <v>-3.111008742512311</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-4.668113335866614</v>
+        <v>-4.763534513530864</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-6.188494346516975</v>
+        <v>-6.306355351666021</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.4370293077209411</v>
+        <v>-0.4366894424365384</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.9758371728162771</v>
+        <v>-0.9826575248709801</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3.305335840763533</v>
+        <v>3.383428920650836</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-3.528476369840583</v>
+        <v>-3.591952832505491</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.76111920842667</v>
+        <v>2.827336123279146</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.828268660541809</v>
+        <v>3.91464437016942</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>5.238205005442808</v>
+        <v>5.356147179864081</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>4.534403457221764</v>
+        <v>4.641137933783895</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>4.564308514881027</v>
+        <v>4.675521091128807</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>3.025190360124853</v>
+        <v>3.105841192827853</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>4.396014286055248</v>
+        <v>4.504987812460193</v>
       </c>
     </row>
     <row r="20">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-6.710305790089492</v>
+        <v>-6.941431338551354</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-8.874074053369959</v>
+        <v>-9.195797504226498</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-11.02626883812638</v>
+        <v>-11.4107886654167</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-7.28929759974762</v>
+        <v>-7.535368689662782</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.549721370596991</v>
+        <v>-3.654552932894426</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-8.081065416433361</v>
+        <v>-8.351585815020968</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-6.952853103161345</v>
+        <v>-7.189423856788913</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-8.616272319534289</v>
+        <v>-8.90766539805896</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-8.675108816716644</v>
+        <v>-8.971056564670754</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-8.296900618264033</v>
+        <v>-8.573648971783555</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-7.293121923743769</v>
+        <v>-7.528402296101703</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-10.88630246140166</v>
+        <v>-11.24401913875599</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-13.70591236361896</v>
+        <v>-14.16427374970089</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-15.87915798448638</v>
+        <v>-16.4145524174246</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>6.729862650663804</v>
+        <v>6.859555683548123</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.205667678476253</v>
+        <v>2.242092285331331</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>8.606915476733818</v>
+        <v>8.77117103709616</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>13.14571095022631</v>
+        <v>13.3995046162459</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>9.697196693082788</v>
+        <v>9.891100020904105</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>9.993514934286196</v>
+        <v>10.18958335673615</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>9.469160081294298</v>
+        <v>9.652253768235049</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>7.06948685604565</v>
+        <v>7.209215504470826</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.127362092032051</v>
+        <v>3.191288815911967</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.3474086632636855</v>
+        <v>0.3619945925723655</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.1431924074328776</v>
+        <v>0.1572412682547863</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-6.627310540796316</v>
+        <v>-6.739068643706254</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-6.067229089784746</v>
+        <v>-6.169224244750616</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-8.737033203893787</v>
+        <v>-8.889799942177078</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.77012757126289</v>
+        <v>1.802797458904578</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>7.910491942794756</v>
+        <v>8.029207872534272</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.864460445500498</v>
+        <v>2.914155485856476</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>9.196263965704894</v>
+        <v>9.349030200873521</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>7.107455153733497</v>
+        <v>7.230772476098309</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.978540502302053</v>
+        <v>2.019953035932225</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.206968408768859</v>
+        <v>-1.217551611807572</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.801223017643579</v>
+        <v>-2.835893612206675</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.085587544847286</v>
+        <v>-2.11220700326318</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-7.151305876540938</v>
+        <v>-7.254751333988565</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.703000190289224</v>
+        <v>-2.735095209487064</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.667709929920321</v>
+        <v>-2.700712052141995</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-3.856595511361185</v>
+        <v>-3.908368237889505</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.833707693468746</v>
+        <v>-2.871245330810247</v>
       </c>
     </row>
     <row r="23">
@@ -1456,49 +1456,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.251014077785733</v>
+        <v>-3.272537675201455</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>4.228321400159103</v>
+        <v>4.261281930368042</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>5.348604208714029</v>
+        <v>5.393130781023359</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.339324476860121</v>
+        <v>-1.341164284487149</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.910133095946328</v>
+        <v>1.933894588019633</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.8227279966410492</v>
+        <v>-0.8228086899581442</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.665037471489079</v>
+        <v>-1.673978291010414</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-3.647372385422095</v>
+        <v>-3.671666453387481</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-4.049798318675521</v>
+        <v>-4.078485618816984</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-7.922942151722204</v>
+        <v>-7.982045918348724</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-8.886446133983718</v>
+        <v>-8.950158021292083</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-11.12432028921823</v>
+        <v>-11.20585119982452</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-13.0559667341361</v>
+        <v>-13.15282336802167</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-16.59553407018079</v>
+        <v>-16.71989592887515</v>
       </c>
     </row>
     <row r="24">
@@ -2185,10 +2185,8 @@
           <t>X &gt; -0.356</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4065~4078</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4065</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.01673405341252732</v>
@@ -2239,10 +2237,8 @@
           <t>X &gt; -0.3437</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4045~4058</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4045</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.004527526715641272</v>
@@ -2293,10 +2289,8 @@
           <t>X &gt; -0.3315</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4033~4046</t>
-        </is>
+      <c r="B8" t="n">
+        <v>4033</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.02757008315137455</v>
@@ -2347,10 +2341,8 @@
           <t>X &gt; -0.3192</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>4028~4041</t>
-        </is>
+      <c r="B9" t="n">
+        <v>4028</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.04306254591227088</v>
@@ -2401,10 +2393,8 @@
           <t>X &gt; -0.3069</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>4016~4029</t>
-        </is>
+      <c r="B10" t="n">
+        <v>4016</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.0009771675040965988</v>
@@ -2455,10 +2445,8 @@
           <t>X &gt; -0.2946</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>4006~4019</t>
-        </is>
+      <c r="B11" t="n">
+        <v>4006</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.04257989771681281</v>
@@ -2509,10 +2497,8 @@
           <t>X &gt; -0.2823</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3979~3992</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3979</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.1637790015726992</v>
@@ -2563,10 +2549,8 @@
           <t>X &gt; -0.2701</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3945~3958</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3945</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.2195626254146319</v>
@@ -2617,10 +2601,8 @@
           <t>X &gt; -0.2578</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3913~3926</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3913</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.2264999605563816</v>
@@ -2671,10 +2653,8 @@
           <t>X &gt; -0.2455</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3864~3877</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3864</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.236538655520782</v>
@@ -2725,10 +2705,8 @@
           <t>X &gt; -0.2332</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3817~3829</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3817</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.3649452410770451</v>
@@ -2779,10 +2757,8 @@
           <t>X &gt; -0.221</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3761~3773</t>
-        </is>
+      <c r="B17" t="n">
+        <v>3761</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.2538411826536517</v>
@@ -2833,10 +2809,8 @@
           <t>X &gt; -0.2087</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3698~3708</t>
-        </is>
+      <c r="B18" t="n">
+        <v>3698</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.2820035845033928</v>
@@ -2887,10 +2861,8 @@
           <t>X &gt; -0.1964</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3619~3629</t>
-        </is>
+      <c r="B19" t="n">
+        <v>3619</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.3578637817696304</v>
@@ -2941,10 +2913,8 @@
           <t>X &gt; -0.1841</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3532~3540</t>
-        </is>
+      <c r="B20" t="n">
+        <v>3532</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.2900484897015048</v>
@@ -2995,10 +2965,8 @@
           <t>X &gt; -0.1719</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3452~3457</t>
-        </is>
+      <c r="B21" t="n">
+        <v>3452</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.1359028848614088</v>
@@ -3049,10 +3017,8 @@
           <t>X &gt; -0.1596</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3351~3354</t>
-        </is>
+      <c r="B22" t="n">
+        <v>3351</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.3467478014264316</v>
@@ -3103,10 +3069,8 @@
           <t>X &gt; -0.1473</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3224~3225</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3224</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.4314228163340061</v>
@@ -3157,10 +3121,8 @@
           <t>X &gt; -0.135</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3093~3093</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3093</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.3110910845164696</v>
@@ -3211,10 +3173,8 @@
           <t>X &gt; -0.1228</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2948~2948</t>
-        </is>
+      <c r="B25" t="n">
+        <v>2948</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.01718323201458816</v>
@@ -3265,10 +3225,8 @@
           <t>X &gt; -0.1105</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2769~2769</t>
-        </is>
+      <c r="B26" t="n">
+        <v>2769</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>0.4859766310359674</v>
@@ -3319,10 +3277,8 @@
           <t>X &gt; -0.09821</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2594~2594</t>
-        </is>
+      <c r="B27" t="n">
+        <v>2594</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0.667702774624253</v>
@@ -3373,10 +3329,8 @@
           <t>X &gt; -0.08593</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2441~2441</t>
-        </is>
+      <c r="B28" t="n">
+        <v>2441</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.9682577060087851</v>
@@ -3427,10 +3381,8 @@
           <t>X &gt; -0.07366</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2247~2247</t>
-        </is>
+      <c r="B29" t="n">
+        <v>2247</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>1.667665373603995</v>
@@ -3481,10 +3433,8 @@
           <t>X &gt; -0.06138</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2035~2035</t>
-        </is>
+      <c r="B30" t="n">
+        <v>2035</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>1.806315979544323</v>
@@ -3535,10 +3485,8 @@
           <t>X &gt; -0.0491</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1783~1783</t>
-        </is>
+      <c r="B31" t="n">
+        <v>1783</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>2.07750952050791</v>
@@ -3589,10 +3537,8 @@
           <t>X &gt; -0.03683</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1509~1509</t>
-        </is>
+      <c r="B32" t="n">
+        <v>1509</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>2.443606080055105</v>
@@ -3643,10 +3589,8 @@
           <t>X &gt; -0.02455</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1207~1207</t>
-        </is>
+      <c r="B33" t="n">
+        <v>1207</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>1.856188854603609</v>
@@ -3697,10 +3641,8 @@
           <t>X &gt; -0.01228</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>875~875</t>
-        </is>
+      <c r="B34" t="n">
+        <v>875</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>2.135133108361451</v>
@@ -3751,10 +3693,8 @@
           <t>X &gt; 0</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>0~0</t>
-        </is>
+      <c r="B35" t="n">
+        <v>0</v>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
       <c r="D35" s="4" t="inlineStr"/>
@@ -3911,10 +3851,8 @@
           <t>X &lt; -0.356</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>2.268466441694791</v>
@@ -3965,10 +3903,8 @@
           <t>X &lt; -0.3437</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>104~104</t>
-        </is>
+      <c r="B7" t="n">
+        <v>104</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>1.352715525943871</v>
@@ -4019,10 +3955,8 @@
           <t>X &lt; -0.3315</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>116~116</t>
-        </is>
+      <c r="B8" t="n">
+        <v>116</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.09276857634174718</v>
@@ -4073,10 +4007,8 @@
           <t>X &lt; -0.3192</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>121~121</t>
-        </is>
+      <c r="B9" t="n">
+        <v>121</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.4273226177306313</v>
@@ -4127,10 +4059,8 @@
           <t>X &lt; -0.3069</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>133~133</t>
-        </is>
+      <c r="B10" t="n">
+        <v>133</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.8900203264065709</v>
@@ -4181,10 +4111,8 @@
           <t>X &lt; -0.2946</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>143~143</t>
-        </is>
+      <c r="B11" t="n">
+        <v>143</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>2.052016225244564</v>
@@ -4235,10 +4163,8 @@
           <t>X &lt; -0.2823</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>170~170</t>
-        </is>
+      <c r="B12" t="n">
+        <v>170</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>4.565385209201786</v>
@@ -4289,10 +4215,8 @@
           <t>X &lt; -0.2701</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>204~204</t>
-        </is>
+      <c r="B13" t="n">
+        <v>204</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>4.859502856260612</v>
@@ -4343,10 +4267,8 @@
           <t>X &lt; -0.2578</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>236~236</t>
-        </is>
+      <c r="B14" t="n">
+        <v>236</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>4.286222696739181</v>
@@ -4397,10 +4319,8 @@
           <t>X &lt; -0.2455</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>285~285</t>
-        </is>
+      <c r="B15" t="n">
+        <v>285</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>3.646912556983004</v>
@@ -4451,10 +4371,8 @@
           <t>X &lt; -0.2332</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>332~333</t>
-        </is>
+      <c r="B16" t="n">
+        <v>332</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>4.563618736847083</v>
@@ -4505,10 +4423,8 @@
           <t>X &lt; -0.221</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>388~389</t>
-        </is>
+      <c r="B17" t="n">
+        <v>388</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>2.776484558967404</v>
@@ -4559,10 +4475,8 @@
           <t>X &lt; -0.2087</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>451~454</t>
-        </is>
+      <c r="B18" t="n">
+        <v>451</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>2.572640974944207</v>
@@ -4613,10 +4527,8 @@
           <t>X &lt; -0.1964</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>530~533</t>
-        </is>
+      <c r="B19" t="n">
+        <v>530</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>2.666036351459823</v>
@@ -4667,10 +4579,8 @@
           <t>X &lt; -0.1841</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>617~622</t>
-        </is>
+      <c r="B20" t="n">
+        <v>617</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>1.847397692651761</v>
@@ -4721,10 +4631,8 @@
           <t>X &lt; -0.1719</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>697~705</t>
-        </is>
+      <c r="B21" t="n">
+        <v>697</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.8398950131233605</v>
@@ -4775,10 +4683,8 @@
           <t>X &lt; -0.1596</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>798~808</t>
-        </is>
+      <c r="B22" t="n">
+        <v>798</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>1.59072009563161</v>
@@ -4829,10 +4735,8 @@
           <t>X &lt; -0.1473</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>925~937</t>
-        </is>
+      <c r="B23" t="n">
+        <v>925</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>1.615419737420766</v>
@@ -4883,10 +4787,8 @@
           <t>X &lt; -0.135</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1056~1069</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1056</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>1.014513036197883</v>
@@ -4937,10 +4839,8 @@
           <t>X &lt; -0.1228</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1201~1214</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1201</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>0.1424760125742068</v>
@@ -4991,10 +4891,8 @@
           <t>X &lt; -0.1105</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1380~1393</t>
-        </is>
+      <c r="B26" t="n">
+        <v>1380</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.8782193683076116</v>
@@ -5045,10 +4943,8 @@
           <t>X &lt; -0.09821</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1555~1568</t>
-        </is>
+      <c r="B27" t="n">
+        <v>1555</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-1.026601585516097</v>
@@ -5099,10 +4995,8 @@
           <t>X &lt; -0.08593</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1708~1721</t>
-        </is>
+      <c r="B28" t="n">
+        <v>1708</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-1.302270394585335</v>
@@ -5153,10 +5047,8 @@
           <t>X &lt; -0.07366</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1902~1915</t>
-        </is>
+      <c r="B29" t="n">
+        <v>1902</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-1.892916126998493</v>
@@ -5207,10 +5099,8 @@
           <t>X &lt; -0.06138</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2114~2127</t>
-        </is>
+      <c r="B30" t="n">
+        <v>2114</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-1.670683266143214</v>
@@ -5261,10 +5151,8 @@
           <t>X &lt; -0.0491</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2366~2379</t>
-        </is>
+      <c r="B31" t="n">
+        <v>2366</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-1.505628316006529</v>
@@ -5315,10 +5203,8 @@
           <t>X &lt; -0.03683</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2640~2653</t>
-        </is>
+      <c r="B32" t="n">
+        <v>2640</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-1.34379640539656</v>
@@ -5369,10 +5255,8 @@
           <t>X &lt; -0.02455</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2942~2955</t>
-        </is>
+      <c r="B33" t="n">
+        <v>2942</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.7167885740170803</v>
@@ -5423,10 +5307,8 @@
           <t>X &lt; -0.01228</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3274~3287</t>
-        </is>
+      <c r="B34" t="n">
+        <v>3274</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.5311626889352539</v>
@@ -5477,10 +5359,8 @@
           <t>X &lt; 0</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>3603~3616</t>
-        </is>
+      <c r="B35" t="n">
+        <v>3603</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.3916684087055486</v>

--- a/workspaces/btc_daily_14days/drawdown/drawdown_30.xlsx
+++ b/workspaces/btc_daily_14days/drawdown/drawdown_30.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Drawdown-30 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Drawdown-30 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>20</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-2.485504077856717</v>
+        <v>-2.502146090758991</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.092714761686061</v>
+        <v>-4.0810639865946</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-4.488103662688097</v>
+        <v>-4.475319130029035</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-4.35924874278129</v>
+        <v>-4.346825099691813</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-14.87533134933216</v>
+        <v>-14.81391032456329</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-14.58173328182963</v>
+        <v>-14.54489314440521</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-14.67004677602565</v>
+        <v>-14.60915137019971</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-25.12520676843878</v>
+        <v>-25.06298329673404</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-20.19845326168493</v>
+        <v>-20.11218114533437</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-11.06272479346087</v>
+        <v>-10.95011870939301</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-16.26640030233061</v>
+        <v>-16.15315635205704</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-16.23606976056917</v>
+        <v>-16.09901357240049</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-16.66016701745638</v>
+        <v>-16.49797462185484</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-21.41455241742233</v>
+        <v>-21.25298329355609</v>
       </c>
     </row>
     <row r="7">
@@ -624,101 +624,101 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-10.79199924285736</v>
+        <v>-14.00356970237342</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-20.70984038769073</v>
+        <v>-23.2548379872803</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-37.73067450098972</v>
+        <v>-38.99670729976125</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-29.2973313249044</v>
+        <v>-31.20340689321307</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-38.15645118540326</v>
+        <v>-39.37437010482252</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-37.86864478423616</v>
+        <v>-39.11144493230781</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-29.6438563306694</v>
+        <v>-31.50278119182254</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-30.11748353292784</v>
+        <v>-31.97550141521589</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-30.18587221740607</v>
+        <v>-32.02033175357696</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-31.04282150544751</v>
+        <v>-32.85144465040236</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-22.92801640808788</v>
+        <v>-25.37698603057492</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-22.89936896418241</v>
+        <v>-25.32515581154808</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-23.32514848776493</v>
+        <v>-25.72642876341684</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-23.08121908409127</v>
+        <v>-25.48375252432532</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.3254</t>
+          <t>X ≈ -0.3252</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-12.45315791702808</v>
+        <v>-2.501929021985937</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-34.00330955032978</v>
+        <v>-29.0066927664167</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-34.40598773750219</v>
+        <v>-29.40698850986819</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-34.28464459012132</v>
+        <v>-29.28475588375679</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-34.83019146496105</v>
+        <v>-29.77999130590958</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-34.54160150195318</v>
+        <v>-29.51473739007993</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-34.63496531929925</v>
+        <v>-29.58280138942361</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-35.10985693741731</v>
+        <v>-30.05507601397971</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-35.17951464819148</v>
+        <v>-30.09946461092328</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-36.03773121106867</v>
+        <v>-30.93013313738778</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-36.25135472941024</v>
+        <v>-31.14185676143549</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-16.23596307841407</v>
+        <v>-6.103849548708673</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-16.66011205289441</v>
+        <v>-6.500391654062931</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-16.4145524174246</v>
+        <v>-6.252983293544723</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>12</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>14.12763585318109</v>
+        <v>14.11115295232432</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>29.1417737682414</v>
+        <v>29.15371619520679</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>28.75474304124089</v>
+        <v>28.76779417911898</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>20.57910223293135</v>
+        <v>20.5917072642352</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>11.73245621373411</v>
+        <v>11.79404776875578</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>20.34934608498591</v>
+        <v>20.38638795813954</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>11.95075670692206</v>
+        <v>12.01178515635691</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>11.48741523355539</v>
+        <v>11.5497959846382</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>11.4293093977546</v>
+        <v>11.51569407655428</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>10.58265285243102</v>
+        <v>10.69531962736606</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>10.38059181001709</v>
+        <v>10.4938922379767</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-6.240906594338348</v>
+        <v>-6.103837555944793</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.668674956197123</v>
+        <v>1.830879840275045</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>10.25211424924206</v>
+        <v>10.41368337310679</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>10</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>17.44993749499997</v>
+        <v>17.4334884749703</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5.877652966533503</v>
+        <v>5.889390499334098</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.484873749308356</v>
+        <v>5.497736943341074</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.616171967566586</v>
+        <v>5.62866722021252</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5.080590155267537</v>
+        <v>5.142137250135626</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-4.601047795656505</v>
+        <v>-4.5641535526333</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-4.686950543212355</v>
+        <v>-4.626008702870664</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.830626930381925</v>
+        <v>4.892977961663071</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>14.75841161582807</v>
+        <v>14.84480852621358</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-6.06744557480949</v>
+        <v>-5.954828701355964</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>13.71138865137341</v>
+        <v>13.82469629397249</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>13.74913045056647</v>
+        <v>13.88622879201377</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>13.33242793969612</v>
+        <v>13.4946413006512</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>13.5854475825754</v>
+        <v>13.74701670643936</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>27</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>17.81857692608172</v>
+        <v>17.80213516808394</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5.138978748014843</v>
+        <v>5.150710220011803</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4.74603377561877</v>
+        <v>4.758891357594059</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4.877156468231711</v>
+        <v>4.889646644495244</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8.036760984779946</v>
+        <v>8.098327441980778</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.639721272615581</v>
+        <v>4.676670018756496</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>11.95052489461056</v>
+        <v>12.01155309295497</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>4.090937889804685</v>
+        <v>4.153285045840406</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>7.73003843298077</v>
+        <v>7.816408780057671</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.5174116603556627</v>
+        <v>-0.4047794569340439</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>6.679558388867001</v>
+        <v>6.79284985326283</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.013722042477923</v>
+        <v>3.150803890307692</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.108417910038895</v>
+        <v>-0.9462156652564886</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.858996861867368</v>
+        <v>-0.6974277379988578</v>
       </c>
     </row>
     <row r="12">
@@ -887,98 +887,98 @@
         <v>34</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>6.308762058910567</v>
+        <v>6.292211944098433</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.772077861458499</v>
+        <v>1.783779212566991</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>10.17730629056045</v>
+        <v>10.19021035469409</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.442335926971026</v>
+        <v>4.454823437602435</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.9719876199428938</v>
+        <v>1.033504771505939</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>7.139959604201501</v>
+        <v>7.176923319925251</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-7.622908823498641</v>
+        <v>-7.561985556249994</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>6.592490226558539</v>
+        <v>6.654847921346779</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.279207429741668</v>
+        <v>-2.192876381793951</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.1909347615512615</v>
+        <v>-0.07830343906186954</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.334690053731975</v>
+        <v>-3.221422569732887</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.3614966115870857</v>
+        <v>-0.2244209124667265</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5.099163528517437</v>
+        <v>5.261369861816313</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.408976994340108</v>
+        <v>2.570546118208618</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.264</t>
+          <t>X ≈ -0.2639</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.6287433873880843</v>
+        <v>-0.9923945187860426</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2.138512402477552</v>
+        <v>3.471931068069836</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>7.977124959022944</v>
+        <v>9.123193667137258</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>8.109240351455192</v>
+        <v>9.255226784953251</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4.456580951313072</v>
+        <v>5.746361194977155</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>10.99213957762433</v>
+        <v>12.06866907783203</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>17.14918216304492</v>
+        <v>18.06098468942872</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>13.56692662015546</v>
+        <v>14.57483497279605</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>10.38848238727937</v>
+        <v>11.51519832936655</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>12.66357807606526</v>
+        <v>13.72224957494437</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>12.46206526586037</v>
+        <v>13.52161179781679</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>9.376176219536234</v>
+        <v>10.55440066572269</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>12.08265155981076</v>
+        <v>13.19159039216212</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>15.46044758257256</v>
+        <v>16.47428943371664</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.5651228423506467</v>
+        <v>1.650310689838342</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.9939719446538007</v>
+        <v>0.07314251121584903</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.634708817990209</v>
+        <v>1.757188253376505</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>8.872129136608429</v>
+        <v>8.121287266662755</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>12.40977780959849</v>
+        <v>11.79264978968781</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>6.600255803542503</v>
+        <v>5.831033732856824</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>8.554419619253743</v>
+        <v>7.851480915560295</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>10.12795830879519</v>
+        <v>9.468642356498215</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>10.06974489515192</v>
+        <v>9.434248462746872</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>5.145582719885155</v>
+        <v>4.451225281822779</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>4.942193645469736</v>
+        <v>4.248270591058514</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>4.977841867611133</v>
+        <v>4.30751127492077</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>4.559024010392761</v>
+        <v>3.913611029627717</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>4.809937378495619</v>
+        <v>4.163683373110572</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>10.1917153246551</v>
+        <v>9.955283499370161</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>10.67056582698759</v>
+        <v>10.45725121341443</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>8.154685703226434</v>
+        <v>7.989135285042643</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>8.290296672893582</v>
+        <v>8.120747738753828</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>11.98842366272062</v>
+        <v>11.79195862774601</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>12.29129750721756</v>
+        <v>12.06769834713457</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>14.3338390287829</v>
+        <v>14.08971595453569</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>13.85985519531976</v>
+        <v>13.62842295581974</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>18.0504667500716</v>
+        <v>17.75641031364172</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>15.06184447988231</v>
+        <v>14.85690474238298</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>21.23929703767094</v>
+        <v>20.90180166010532</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>14.8992972287739</v>
+        <v>14.71868115073823</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>20.85575047203864</v>
+        <v>20.57589918888174</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>15.92587311448932</v>
+        <v>14.58035003977819</v>
       </c>
     </row>
     <row r="16">
@@ -1095,150 +1095,150 @@
         <v>56</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-7.82677316483403</v>
+        <v>-7.841477859524787</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3.028594608503475</v>
+        <v>3.039469320098497</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>9.758794798826969</v>
+        <v>9.769001833492737</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>17.01714756861785</v>
+        <v>17.02510311964807</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>14.70268732065543</v>
+        <v>14.76028595066244</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>7.874333007963543</v>
+        <v>7.909152236538262</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.6602481738151269</v>
+        <v>0.720950837717794</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.1940371028464014</v>
+        <v>0.2562442260018898</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.700886372856949</v>
+        <v>3.786194048549099</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>6.421082738382722</v>
+        <v>6.531971302541905</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.8637828537089121</v>
+        <v>0.9767177819632451</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>11.60994349374776</v>
+        <v>11.74385343495477</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>9.40715482172849</v>
+        <v>9.566764021971942</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>9.656876154003967</v>
+        <v>9.818445277871668</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.2148</t>
+          <t>X ≈ -0.2147</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.399247103701015</v>
+        <v>1.330495225056332</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-8.178363471999042</v>
+        <v>-7.914412289124421</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-5.408061856540733</v>
+        <v>-5.242368061799525</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-6.855151662379015</v>
+        <v>-6.648809995765447</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.659822106498979</v>
+        <v>-2.534071887455241</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.8077547105337501</v>
+        <v>0.8085285583099022</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.8651368393642187</v>
+        <v>-0.7872531814809491</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.822703264577541</v>
+        <v>1.819621652032026</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.411906819760553</v>
+        <v>-1.28955067680274</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.875588648167678</v>
+        <v>-3.649582890126382</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.678433055631217</v>
+        <v>0.7570793279283592</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.01447220745571798</v>
+        <v>-0.7221579058462879</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>5.240488155060298</v>
+        <v>3.49688680569664</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>7.077511074638885</v>
+        <v>5.285478244905448</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.2026</t>
+          <t>X ≈ -0.2025</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>79</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>3.193161654819285</v>
+        <v>3.777342724102652</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.3244487294789948</v>
+        <v>0.9158592260069724</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.07040494027187805</v>
+        <v>-0.7395699313949962</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-7.520806594384666</v>
+        <v>-6.920625692462359</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.049603014818111</v>
+        <v>1.424448668018215</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>4.875834020488327</v>
+        <v>5.488365198694616</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>6.057105439914181</v>
+        <v>6.692003753327903</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>6.856871856998815</v>
+        <v>7.486557846836604</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>4.267650165923889</v>
+        <v>4.922077321536825</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>11.01185484570267</v>
+        <v>11.67828782620687</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>8.278559729215033</v>
+        <v>8.384619074660634</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>12.11041124099056</v>
+        <v>12.24051503120192</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>11.69015663004594</v>
+        <v>11.84897200055715</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>10.67405517751212</v>
+        <v>10.83562430138063</v>
       </c>
     </row>
     <row r="19">
@@ -1248,153 +1248,153 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.111008742512311</v>
+        <v>-4.868784224053876</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-4.763534513530864</v>
+        <v>-6.555650173618126</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-6.306355351666021</v>
+        <v>-6.95052779108709</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.4366894424365384</v>
+        <v>-1.204094049075891</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.9826575248709801</v>
+        <v>-1.711096264599135</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3.383428920650836</v>
+        <v>3.060046540544633</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-3.591952832505491</v>
+        <v>-3.743182985892943</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.827336123279146</v>
+        <v>3.117408285306155</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.91464437016942</v>
+        <v>3.689989966619237</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>5.356147179864081</v>
+        <v>4.588974744094628</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>4.641137933783895</v>
+        <v>4.383612425105277</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>4.675521091128807</v>
+        <v>3.944713806146837</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>3.105841192827853</v>
+        <v>1.92414949105747</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>4.504987812460193</v>
+        <v>3.297578504196466</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.178</t>
+          <t>X ≈ -0.1779</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-6.941431338551354</v>
+        <v>-6.853307582542001</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-9.195797504226498</v>
+        <v>-9.725826661062626</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-11.4107886654167</v>
+        <v>-11.34074596738251</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-7.535368689662782</v>
+        <v>-7.546886330625497</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.654552932894426</v>
+        <v>-4.391571103188831</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-8.351585815020968</v>
+        <v>-9.549119804022546</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-7.189423856788913</v>
+        <v>-8.954229496984468</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-8.90766539805896</v>
+        <v>-10.64336389716361</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-8.971056564670754</v>
+        <v>-10.68171448618208</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-8.573648971783555</v>
+        <v>-10.29429875116378</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-7.528402296101703</v>
+        <v>-9.279615993518895</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-11.24401913875599</v>
+        <v>-12.87722988175706</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-14.16427374970089</v>
+        <v>-15.71623512814968</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-16.4145524174246</v>
+        <v>-17.22859304965365</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ -0.1658</t>
+          <t>X ≈ -0.1657</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>6.859555683548123</v>
+        <v>6.705076336629013</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.242092285331331</v>
+        <v>2.215702842542697</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>8.77117103709616</v>
+        <v>8.614602890757624</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>13.3995046162459</v>
+        <v>12.62929958537542</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>9.891100020904105</v>
+        <v>9.231277904817851</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>10.18958335673615</v>
+        <v>9.504063423636779</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>9.652253768235049</v>
+        <v>8.47253354800376</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>7.209215504470826</v>
+        <v>6.064953214804881</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.191288815911967</v>
+        <v>2.144485460036798</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.3619945925723655</v>
+        <v>-0.6210906935937217</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.1572412682547863</v>
+        <v>-0.825231141129585</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-6.739068643706254</v>
+        <v>-7.56318090861906</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-6.169224244750616</v>
+        <v>-6.987465048775562</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-8.889799942177078</v>
+        <v>-9.651041545983055</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.802797458904578</v>
+        <v>1.750902349996117</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>8.029207872534272</v>
+        <v>7.91510391724055</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.914155485856476</v>
+        <v>2.875335439972865</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>9.349030200873521</v>
+        <v>9.20568450585327</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>7.230772476098309</v>
+        <v>7.169111877874208</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.019953035932225</v>
+        <v>2.015540807546031</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.217551611807572</v>
+        <v>-1.145890475478062</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.835893612206675</v>
+        <v>-3.162110832760625</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.11220700326318</v>
+        <v>-2.423889643447801</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-7.254751333988565</v>
+        <v>-7.898881014960466</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.735095209487064</v>
+        <v>-3.451858671798874</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.700712052141995</v>
+        <v>-3.393691934433981</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-3.908368237889505</v>
+        <v>-4.564043659447243</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.871245330810247</v>
+        <v>-3.53980499898244</v>
       </c>
     </row>
     <row r="23">
@@ -1456,49 +1456,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.272537675201455</v>
+        <v>-3.263969176816452</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>4.261281930368042</v>
+        <v>4.235901891374873</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>5.393130781023359</v>
+        <v>5.357707073791602</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.341164284487149</v>
+        <v>-1.326757247712251</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.933894588019633</v>
+        <v>1.971789820087039</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.8228086899581442</v>
+        <v>-0.7857276913970708</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.673978291010414</v>
+        <v>-1.603959538198282</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-3.671666453387481</v>
+        <v>-3.58494381373314</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-4.078485618816984</v>
+        <v>-4.379492180445695</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-7.982045918348724</v>
+        <v>-8.233623791563708</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-8.950158021292083</v>
+        <v>-9.195339996675379</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-11.20585119982452</v>
+        <v>-11.40990053203777</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-13.15282336802167</v>
+        <v>-13.32020997375328</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-16.71989592887515</v>
+        <v>-16.85904389961687</v>
       </c>
     </row>
     <row r="24">
@@ -1508,523 +1508,523 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-6.28654176848584</v>
+        <v>-5.927085503173124</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-5.139494691794923</v>
+        <v>-4.773582212994967</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-3.465397881150132</v>
+        <v>-3.115518185868552</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-7.47307578302555</v>
+        <v>-7.09482124908412</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.873565963614801</v>
+        <v>-3.476528984396147</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-3.576124025899141</v>
+        <v>-3.203743465577219</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-7.798788777654181</v>
+        <v>-7.373988595898574</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-11.71424803850465</v>
+        <v>-11.26447889052834</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-11.77524792468695</v>
+        <v>-11.30145149966529</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-10.55640759247349</v>
+        <v>-10.07048555993232</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-9.381850571963646</v>
+        <v>-8.904762993769943</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-13.48539844910113</v>
+        <v>-12.95618529750094</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-12.52634271521813</v>
+        <v>-11.98148021036598</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-12.27662138294153</v>
+        <v>-11.73243534835046</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ -0.1167</t>
+          <t>X ≈ -0.1166</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-7.800700890042499</v>
+        <v>-8.1163438852941</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-11.08825215663792</v>
+        <v>-11.38431655186075</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-17.62837225988255</v>
+        <v>-17.95761451903214</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-16.93945990939783</v>
+        <v>-17.27252835355892</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-14.68458503508465</v>
+        <v>-14.95875154865658</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-11.59384700798339</v>
+        <v>-11.87697726579258</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-12.23723994313289</v>
+        <v>-12.49943110782716</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-14.38040099554568</v>
+        <v>-14.6506571266376</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-13.88274166385089</v>
+        <v>-14.12583198296527</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-14.73286684887881</v>
+        <v>-14.94966056378026</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-14.37896095531917</v>
+        <v>-14.59200325850723</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-11.55128170858814</v>
+        <v>-11.72484775709739</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-10.8542178837791</v>
+        <v>-10.99641017804337</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-7.252541244240376</v>
+        <v>-7.376578799174069</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ -0.1044</t>
+          <t>X ≈ -0.1043</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>175</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-2.207724034495563</v>
+        <v>-1.953215938768793</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-10.6764405046028</v>
+        <v>-10.39803823658394</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-4.785594925485107</v>
+        <v>-4.513843154133944</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-8.655341792877735</v>
+        <v>-8.383754512635413</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-9.193763007949777</v>
+        <v>-9.132106283809065</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-8.896321070234244</v>
+        <v>-8.859320764990265</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-10.12391193036354</v>
+        <v>-10.06283399707274</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-7.162523900573611</v>
+        <v>-7.100095328884656</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-4.366380929613058</v>
+        <v>-4.279925080878598</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.930791828926694</v>
+        <v>-2.818039375979289</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.421259438958693</v>
+        <v>-1.3078941092298</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.8154477101846922</v>
+        <v>-0.6782988004363375</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.6642737497008824</v>
+        <v>-0.5020281555714519</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.7283047254325368</v>
+        <v>0.889873849301047</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ -0.09207</t>
+          <t>X ≈ -0.09205</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>153</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-4.127425248314552</v>
+        <v>-4.138146336512712</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-4.431809318795146</v>
+        <v>-4.415246088079314</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-8.094651881600889</v>
+        <v>-8.078124719309272</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-9.271588291477045</v>
+        <v>-9.259103641456583</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-11.11719904903288</v>
+        <v>-11.05554232489217</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-9.512567568833553</v>
+        <v>-9.475567263589575</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-8.290111743622177</v>
+        <v>-8.22903381033138</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-8.757295142403677</v>
+        <v>-8.694866570714723</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-10.12548457106963</v>
+        <v>-10.03902872233517</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-12.28279929858122</v>
+        <v>-12.17004684563382</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-10.52676830917331</v>
+        <v>-10.41340297944442</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-11.14597992306956</v>
+        <v>-11.00883101332121</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-10.25904499153096</v>
+        <v>-10.09679939740153</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-11.31651320173832</v>
+        <v>-11.15494407786981</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ -0.0798</t>
+          <t>X ≈ -0.07977</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>194</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-7.132613577941818</v>
+        <v>-7.13840975347005</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-7.197795438328754</v>
+        <v>-7.178025660582925</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-8.623591979976894</v>
+        <v>-8.606262496891915</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-6.946947094792307</v>
+        <v>-6.934462444771846</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-4.39258480470972</v>
+        <v>-4.330928080569009</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-7.187926372148816</v>
+        <v>-7.150926066904837</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-7.272660089420981</v>
+        <v>-7.211582156130184</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-7.224379570676703</v>
+        <v>-7.161950998987749</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-7.285379456859005</v>
+        <v>-7.198923608124545</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-7.104576806835269</v>
+        <v>-6.991824353887864</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-8.855721883730403</v>
+        <v>-8.74235655400151</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-11.39865831401384</v>
+        <v>-11.26150940426548</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-11.30344900743285</v>
+        <v>-11.14120341330342</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-11.56919159268233</v>
+        <v>-11.40762246881382</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ -0.06752</t>
+          <t>X ≈ -0.0675</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>212</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.336750359035193</v>
+        <v>0.5371645063808614</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>5.800648444184262</v>
+        <v>6.014788515660783</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.405779737587558</v>
+        <v>5.622378527010007</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>6.479429096610367</v>
+        <v>6.491913746630829</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>4.054215428707906</v>
+        <v>4.115872152848617</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>5.295053592838762</v>
+        <v>5.332053898082741</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1.908433083113437</v>
+        <v>1.969511016404233</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2.384645910747253</v>
+        <v>2.447074482436207</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.4368535717346518</v>
+        <v>0.5233094204691113</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>1.473520839536803</v>
+        <v>1.586273292484208</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.561421164025951</v>
+        <v>-1.448055834297058</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.470434233095609</v>
+        <v>-2.333285323347255</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.418990730833073</v>
+        <v>-2.256745136703643</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.225873172141689</v>
+        <v>-1.064304048273179</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ -0.05524</t>
+          <t>X ≈ -0.05523</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>252</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.1124859392575459</v>
+        <v>0.05301184043291585</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.45054362238124</v>
+        <v>1.635341769471928</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.2620241221338873</v>
+        <v>0.274877863547168</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.195024332560145</v>
+        <v>-1.182539682539684</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-5.70169951588624</v>
+        <v>-5.640042791745529</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-6.594733768646812</v>
+        <v>-6.557733463402833</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-3.504864311315821</v>
+        <v>-3.443786378025024</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-3.575222313272207</v>
+        <v>-3.512793741583252</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-3.636222199454316</v>
+        <v>-3.549766350719857</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.311744209879173</v>
+        <v>-1.198991756931768</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.326021343720285</v>
+        <v>-0.212656013991392</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>1.29566340092655</v>
+        <v>1.432812310674905</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.4785833931563417</v>
+        <v>0.6408289872857722</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>2.712431709559617</v>
+        <v>2.874000833428127</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ -0.04297</t>
+          <t>X ≈ -0.04296</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>274</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.0613062053374307</v>
+        <v>0.2103392241785116</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.099367628869558</v>
+        <v>2.111090652000954</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.799389433221926</v>
+        <v>2.812243174635206</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.294606069479009</v>
+        <v>3.30709071949947</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>2.756184854406762</v>
+        <v>2.817841578547473</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>5.608371317669906</v>
+        <v>5.645371622913885</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>5.52363760039767</v>
+        <v>5.584715533688467</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>7.246235223514063</v>
+        <v>7.308663795203017</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>6.090344826382776</v>
+        <v>6.176800675117235</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>4.8752561377053</v>
+        <v>4.988008590652704</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>5.035466317037184</v>
+        <v>5.148831646766077</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>3.974958963433792</v>
+        <v>4.112107873182147</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>3.919667856138531</v>
+        <v>4.081913450267962</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.5751363590304379</v>
+        <v>-0.4135672351619277</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ -0.03069</t>
+          <t>X ≈ -0.03068</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>4.791329891710561</v>
+        <v>4.915630749370436</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.1996238284151701</v>
+        <v>0.03212363121129158</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.8574965338105969</v>
+        <v>-1.021680363704121</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.3961175733884446</v>
+        <v>-0.5617633191890263</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.052216178426804</v>
+        <v>0.9291855596610716</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.018532288327847</v>
+        <v>0.871938075179628</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1.927176054499284</v>
+        <v>1.801380995855119</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>2.784495966976053</v>
+        <v>2.6556802486731</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1.398992769535482</v>
+        <v>1.298575626335023</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.5488675845075548</v>
+        <v>0.4747470455199974</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.6752400880045428</v>
+        <v>0.6006396012842359</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.6148800659083093</v>
+        <v>-0.6613256745521809</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.366260504667736</v>
+        <v>-1.386516604416343</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.778790828020625</v>
+        <v>-1.797537749001634</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ -0.01842</t>
+          <t>X ≈ -0.01841</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.121019511115328</v>
+        <v>0.9642084168048584</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-1.394168559680253</v>
+        <v>-1.223198275601746</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.5842179891684083</v>
+        <v>-0.408477049414941</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-1.357579314392311</v>
+        <v>-1.184937419076462</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-1.293590890910224</v>
+        <v>-1.06995695277763</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-1.598558591748713</v>
+        <v>-1.401401041209382</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.779677851189696</v>
+        <v>-0.5557127195587128</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-1.849270888525417</v>
+        <v>-1.625775087192814</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.4042466783221741</v>
+        <v>-0.1521736782027574</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.6519622247958878</v>
+        <v>-0.3717726517669462</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.5555107298363566</v>
+        <v>-0.2737982956776577</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.08128206606325961</v>
+        <v>0.3885980489379506</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>1.769461190058109</v>
+        <v>2.108243747751807</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>2.922796980165764</v>
+        <v>3.263633020643304</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ -0.00614</t>
+          <t>X ≈ -0.006135</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -2093,7 +2093,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Drawdown-30 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Drawdown-30 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2182,53 +2182,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.356</t>
+          <t>X &gt; -0.3559</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4065</v>
+        <v>4077</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.01673405341252732</v>
+        <v>-0.0162242943246369</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.05245679383092039</v>
+        <v>0.05197888159326425</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1573879999278347</v>
+        <v>-0.1572813014886592</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1610385501081097</v>
+        <v>-0.160910902163657</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1706898611652861</v>
+        <v>-0.1718937112616956</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.01743151648680197</v>
+        <v>0.01635680101791337</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.05388667075085607</v>
+        <v>-0.05541829817810395</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.03275981350154922</v>
+        <v>0.03093577569530481</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.08360152036939184</v>
+        <v>0.08096243924459401</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.01564946330510253</v>
+        <v>-0.01872548232577742</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.08371203061469146</v>
+        <v>-0.08660559382350641</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.1584523819327757</v>
+        <v>-0.1617856494538188</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.04843508762514404</v>
+        <v>-0.05278833212859269</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.07998907179113957</v>
+        <v>-0.08423176056614778</v>
       </c>
     </row>
     <row r="7">
@@ -2238,205 +2238,205 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4045</v>
+        <v>4057</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.004527526715641272</v>
+        <v>-0.003969318744481143</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.07295207964311601</v>
+        <v>0.07235375400238553</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.135975314327041</v>
+        <v>-0.135994449979961</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1402810213433483</v>
+        <v>-0.140275387263344</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.09798458804704069</v>
+        <v>-0.09971221452370571</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.08961527321518759</v>
+        <v>0.08814013819032596</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.01838111716149626</v>
+        <v>0.0163279826797833</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.1571502539561322</v>
+        <v>0.1546425495303083</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.1838836206514927</v>
+        <v>0.1805096099844476</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.03897142831495159</v>
+        <v>0.03516356488678696</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.003698738789161382</v>
+        <v>-0.007401498392233918</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.0789586000853717</v>
+        <v>-0.08321908340527528</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.03369955726896023</v>
+        <v>0.02828234221069437</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.02549702633312023</v>
+        <v>0.02012491447940334</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.3315</t>
+          <t>X &gt; -0.3314</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4033</v>
+        <v>4044</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.02757008315137455</v>
+        <v>0.0410343422315762</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.1347902917948716</v>
+        <v>0.1473422536652507</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.02411407201611837</v>
+        <v>-0.01107128799995394</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.05352560263698791</v>
+        <v>-0.04041863415321956</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.01525657217321452</v>
+        <v>0.02654163131553133</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.2025582736340894</v>
+        <v>0.21415265201734</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1066396962276954</v>
+        <v>0.1176505393732796</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.2472309892506033</v>
+        <v>0.2579293624733623</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.2742473870925295</v>
+        <v>0.2840236895409021</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1314538273244139</v>
+        <v>0.140882137290042</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.06451147991443662</v>
+        <v>0.07415255673101484</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.01105755263455421</v>
+        <v>-0.002075369887514</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.1032027004726359</v>
+        <v>0.1110744402258206</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.09424996293741117</v>
+        <v>0.1021106728138363</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.3192</t>
+          <t>X &gt; -0.3191</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4028</v>
+        <v>4040</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.04306254591227088</v>
+        <v>0.04355212774069628</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.177166284647555</v>
+        <v>0.1762076348732577</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.01856451992217245</v>
+        <v>0.01803358053655302</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.0110341441123083</v>
+        <v>-0.0114638447971771</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.05851060399686503</v>
+        <v>0.05605305006525896</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.2456865752423099</v>
+        <v>0.2435871966134755</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.149764826584601</v>
+        <v>0.1470569274215947</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.2911201252072502</v>
+        <v>0.287942239083705</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.3182565256666052</v>
+        <v>0.314106351224531</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.1763510282161604</v>
+        <v>0.1716455187501182</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.1095907577313753</v>
+        <v>0.1050594966499858</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.009082598216714644</v>
+        <v>0.003965990685586007</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.1240111845259619</v>
+        <v>0.117620446259771</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.114742518027235</v>
+        <v>0.1084028450577605</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.3069</t>
+          <t>X &gt; -0.3068</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4016</v>
+        <v>4028</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.0009771675040965988</v>
+        <v>0.00164269132188366</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.09061865272447989</v>
+        <v>0.08987940678885309</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.06730055534072932</v>
+        <v>-0.0676161531235735</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.07255845599591026</v>
+        <v>-0.0728436991438528</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.02362829639805142</v>
+        <v>0.02108385030749815</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.1856158794960692</v>
+        <v>0.1835788527360407</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.11450289865531</v>
+        <v>0.1117101700364813</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.2576650601424575</v>
+        <v>0.2543915327910966</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.2850561684791018</v>
+        <v>0.2807351862036853</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1452565008529731</v>
+        <v>0.1402939573540394</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.0789005155432676</v>
+        <v>0.07410964737096037</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.0277578647283363</v>
+        <v>0.02216202905687936</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.119395655327736</v>
+        <v>0.1125163964265568</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.08445156663914588</v>
+        <v>0.07770191001888094</v>
       </c>
     </row>
     <row r="11">
@@ -2446,49 +2446,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4006</v>
+        <v>4018</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.04257989771681281</v>
+        <v>-0.04174169340596023</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.07617273581531236</v>
+        <v>0.07544558127230516</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.08116020163291182</v>
+        <v>-0.08146720612622005</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.08675898126691095</v>
+        <v>-0.08703362179032581</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.01100482695504468</v>
+        <v>0.008338570566756687</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.1975646155798145</v>
+        <v>0.1953950110371068</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.1264885537772926</v>
+        <v>0.1235014066539719</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.2462497783894975</v>
+        <v>0.2428470170397929</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.2489269736529636</v>
+        <v>0.2444881146755407</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.1607649933034452</v>
+        <v>0.1554635010541645</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.04487034046630356</v>
+        <v>0.03988718184930917</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.006494188656184008</v>
+        <v>-0.01234286582355537</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.0864125492759058</v>
+        <v>0.07921095863605387</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.05074962950500606</v>
+        <v>0.04368171391031694</v>
       </c>
     </row>
     <row r="12">
@@ -2498,153 +2498,153 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3979</v>
+        <v>3991</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.1637790015726992</v>
+        <v>-0.1624594772346342</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.04181843515450367</v>
+        <v>0.04111029055670912</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.1139157274901166</v>
+        <v>-0.114213305154145</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1204422476997919</v>
+        <v>-0.1207019673652994</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.04345494089146484</v>
+        <v>-0.04639199809477645</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.1674218084071768</v>
+        <v>0.1650781918919364</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.04625508275380241</v>
+        <v>0.04307610083334623</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.2201611684351761</v>
+        <v>0.2163920366394905</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.1981629602320396</v>
+        <v>0.1932623923088812</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1653668454393653</v>
+        <v>0.1592536688982307</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.0001501614956964659</v>
+        <v>-0.005798108085095066</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.02698824199637784</v>
+        <v>-0.03374225505321249</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.09452022014835393</v>
+        <v>0.0861481971339515</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.0569228276118352</v>
+        <v>0.04869548369271826</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.2701</t>
+          <t>X &gt; -0.27</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3945</v>
+        <v>3957</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.2195626254146319</v>
+        <v>-0.2179203891187171</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.02690618661348054</v>
+        <v>0.02613663795414567</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.202610670104491</v>
+        <v>-0.2027527048091571</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.1597665716386629</v>
+        <v>-0.1600165652346206</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.05220653710651391</v>
+        <v>-0.05567086849316638</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.1073289604839687</v>
+        <v>0.1048298385047275</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.1123518059002038</v>
+        <v>0.1084215889154407</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1652412221801285</v>
+        <v>0.1610704546126911</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2195141879276292</v>
+        <v>0.2137649746489174</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1684376324197601</v>
+        <v>0.161294846980276</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.02858858535754649</v>
+        <v>0.02183172049615933</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.02410528012918434</v>
+        <v>-0.03210387386744884</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.05138767959460466</v>
+        <v>0.04168078833960465</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.03665163834218532</v>
+        <v>0.02702681511209448</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.2578</t>
+          <t>X &gt; -0.2577</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3913</v>
+        <v>3924</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.2264999605563816</v>
+        <v>-0.2114072274777854</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.009637748354428766</v>
+        <v>-0.002841755571296289</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.2695034736138382</v>
+        <v>-0.2811819174172641</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.2273894240636523</v>
+        <v>-0.2391967463141853</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.08907880892595443</v>
+        <v>-0.1044647161217327</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.01831440905323234</v>
+        <v>0.004216511568493786</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.02697315485333718</v>
+        <v>-0.04255562370355648</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.05564399940087128</v>
+        <v>0.0398537805301018</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.1363537017586438</v>
+        <v>0.1187223394028223</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.06625401519598739</v>
+        <v>0.04725012067476797</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.07309075371122731</v>
+        <v>-0.09169854009292067</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.1009795474405308</v>
+        <v>-0.1211341108211883</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.04700241602689914</v>
+        <v>-0.06890713646318147</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.08948213886594658</v>
+        <v>-0.1112911426896304</v>
       </c>
     </row>
     <row r="15">
@@ -2654,49 +2654,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3864</v>
+        <v>3876</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.236538655520782</v>
+        <v>-0.2344625577231909</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.002844750511691529</v>
+        <v>-0.003782737203330555</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.3063322526740393</v>
+        <v>-0.3064248916685841</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.3427818695794258</v>
+        <v>-0.3427321520476454</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.2475788022768057</v>
+        <v>-0.2517974035001913</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.06515223906529144</v>
+        <v>-0.0679422156301257</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.1357951646699149</v>
+        <v>-0.140314590134075</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.07208462408782168</v>
+        <v>-0.07691140307321831</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.0103867844511214</v>
+        <v>0.00335978679174076</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.00184223814376594</v>
+        <v>-0.00728827141375632</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.1366903747153358</v>
+        <v>-0.1454442878471269</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.1653848914719802</v>
+        <v>-0.1759780165269689</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.105412171434395</v>
+        <v>-0.1182262468791677</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.1516124588324743</v>
+        <v>-0.1642320035664113</v>
       </c>
     </row>
     <row r="16">
@@ -2706,153 +2706,153 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3817</v>
+        <v>3828</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.3649452410770451</v>
+        <v>-0.3622336681569607</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.1342700313978469</v>
+        <v>-0.1349555767095083</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.410515601882139</v>
+        <v>-0.4104444550129216</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.449083858444034</v>
+        <v>-0.4488572917442113</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.3982448006668662</v>
+        <v>-0.4028162879045283</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.2173013451892913</v>
+        <v>-0.220113257169487</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.3139646189775647</v>
+        <v>-0.3187475750202182</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.2436332673972643</v>
+        <v>-0.2487651254417713</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.2117467650338511</v>
+        <v>-0.2192489972439873</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.1835966157628945</v>
+        <v>-0.1936731367905082</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.3999000703878863</v>
+        <v>-0.4093595975393214</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.3508813702908284</v>
+        <v>-0.3627449026368836</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.3635139907278742</v>
+        <v>-0.3777137131583004</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.349579925939139</v>
+        <v>-0.3491170448622611</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.221</t>
+          <t>X &gt; -0.2209</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3761</v>
+        <v>3772</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.2538411826536517</v>
+        <v>-0.2511950481366512</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.1813640010427449</v>
+        <v>-0.1820838360470631</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.561933145737413</v>
+        <v>-0.5615709110458837</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.7091500535824196</v>
+        <v>-0.7082798217118693</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.6230925004259902</v>
+        <v>-0.6279312734187741</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.337783005326628</v>
+        <v>-0.3408022464716183</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.3284703133132112</v>
+        <v>-0.3341831824203467</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.2501500290919338</v>
+        <v>-0.2562626131620505</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.2700045304478067</v>
+        <v>-0.2787147476587322</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.2819380259814963</v>
+        <v>-0.2935236374804973</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.4187158756921718</v>
+        <v>-0.4299376286241881</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.5289739500265895</v>
+        <v>-0.5424823116785404</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.5089958980656917</v>
+        <v>-0.5253517707318096</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.498572624816255</v>
+        <v>-0.5000670687416715</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.2087</t>
+          <t>X &gt; -0.2086</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3698</v>
+        <v>3707</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.2820035845033928</v>
+        <v>-0.2789290291880562</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.04512523233797339</v>
+        <v>-0.04650213940556824</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.4793733542878229</v>
+        <v>-0.4794959677496919</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.6044453209285052</v>
+        <v>-0.6041162227602968</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.5883942945896976</v>
+        <v>-0.5945082521313765</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.3572986559754128</v>
+        <v>-0.3609550660860776</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.3193275358277603</v>
+        <v>-0.3262388743710005</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.2854636465881981</v>
+        <v>-0.2926619865738616</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.2505508137829366</v>
+        <v>-0.2609903518145558</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.2207157465878424</v>
+        <v>-0.2346771709517697</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.4374071635973635</v>
+        <v>-0.4507512520868104</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.5382322269117523</v>
+        <v>-0.5393318089483188</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.6069454641411269</v>
+        <v>-0.5958792882575352</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.6276405731844719</v>
+        <v>-0.6015131020265514</v>
       </c>
     </row>
     <row r="19">
@@ -2862,49 +2862,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3619</v>
+        <v>3628</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.3578637817696304</v>
+        <v>-0.3672546820298379</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.05319274905075133</v>
+        <v>-0.0674576377152718</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.4883008217393936</v>
+        <v>-0.4738328356857409</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.4534664481451287</v>
+        <v>-0.4665737067441782</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.6459797567182477</v>
+        <v>-0.6384712060155664</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.4715339368377087</v>
+        <v>-0.4883244985330677</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.4585201871357469</v>
+        <v>-0.4790616879289402</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.4413753638535667</v>
+        <v>-0.4620551417115237</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.3491796829171889</v>
+        <v>-0.3738520789906161</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.465914165154004</v>
+        <v>-0.4940829688502077</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.6276700496244914</v>
+        <v>-0.64314217155016</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.8143424324835422</v>
+        <v>-0.8176140306605291</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.8753817905961654</v>
+        <v>-0.8668669541385583</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.874347941049912</v>
+        <v>-0.8505577147247791</v>
       </c>
     </row>
     <row r="20">
@@ -2914,101 +2914,101 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3532</v>
+        <v>3539</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.2900484897015048</v>
+        <v>-0.2540486551182326</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.0628320905612938</v>
+        <v>0.0957096795199277</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.3449908715401833</v>
+        <v>-0.3109546635945577</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.4538796982857463</v>
+        <v>-0.4480262892625362</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.637686731285271</v>
+        <v>-0.6114964588514127</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.5664891374610121</v>
+        <v>-0.5775601646754538</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.3813376729377964</v>
+        <v>-0.3969744329080953</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.5218900579024179</v>
+        <v>-0.5520727300145936</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.4542059265804212</v>
+        <v>-0.4760509888689128</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.6093228109684361</v>
+        <v>-0.6219134679889748</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.7574509937231682</v>
+        <v>-0.7695567403838197</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.9495684026291471</v>
+        <v>-0.937378703583903</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.973447022634069</v>
+        <v>-0.9370564041590299</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.006851398172046</v>
+        <v>-0.9548764837227992</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.1719</t>
+          <t>X &gt; -0.1718</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3452</v>
+        <v>3457</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.1359028848614088</v>
+        <v>-0.09751430971795827</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.2774005632099161</v>
+        <v>0.3286764078762374</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.08854132822902727</v>
+        <v>-0.04932814149139375</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.2897663960522081</v>
+        <v>-0.2796414112203678</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.5677709444577133</v>
+        <v>-0.5218331320259324</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.386069747482793</v>
+        <v>-0.3647548738376045</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.223560472848547</v>
+        <v>-0.1939964418018576</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.3275499573194125</v>
+        <v>-0.3127074202933855</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.2568281597648863</v>
+        <v>-0.2339727687995818</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.4247497829078313</v>
+        <v>-0.3924846009885883</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.6005343934362983</v>
+        <v>-0.5676982333670253</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.7109948050364068</v>
+        <v>-0.6541655717903865</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.6677499953555852</v>
+        <v>-0.5864944558317973</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.6497783733921523</v>
+        <v>-0.5688641150776377</v>
       </c>
     </row>
     <row r="22">
@@ -3018,49 +3018,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3351</v>
+        <v>3354</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.3467478014264316</v>
+        <v>-0.3064191506761418</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.2181842504870701</v>
+        <v>0.2707265799780174</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.3555753326748174</v>
+        <v>-0.3153940020524217</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.7023645375747734</v>
+        <v>-0.6760698318075384</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.8830039995163546</v>
+        <v>-0.8213472753756434</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.7048226461775471</v>
+        <v>-0.6678223409335686</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.5212200486018901</v>
+        <v>-0.4601421153110934</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.5547100025718237</v>
+        <v>-0.5085628303754106</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.3607552903358666</v>
+        <v>-0.3070142707584864</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.4484624602947278</v>
+        <v>-0.3854641992180703</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.6233739463550663</v>
+        <v>-0.5597895006599458</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.5293071124951751</v>
+        <v>-0.441992471106623</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.5019341495815155</v>
+        <v>-0.3899232062572011</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.4014220085914104</v>
+        <v>-0.2899540747129166</v>
       </c>
     </row>
     <row r="23">
@@ -3070,49 +3070,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3224</v>
+        <v>3225</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.4314228163340061</v>
+        <v>-0.3887120107030313</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.08950805720523647</v>
+        <v>-0.03504851351248561</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.4843767638018264</v>
+        <v>-0.4430231797334301</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.098309677705956</v>
+        <v>-1.071340005313971</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.202622365646342</v>
+        <v>-1.14096564150563</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.8121571721167342</v>
+        <v>-0.7751568668727558</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.4937901141952139</v>
+        <v>-0.4327121809044172</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.4648494819689617</v>
+        <v>-0.4024209102800071</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.2917620001554155</v>
+        <v>-0.2223392558509119</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.1803487236448831</v>
+        <v>-0.08492752658837333</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.540188896597698</v>
+        <v>-0.4441067338143867</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.4437709997981685</v>
+        <v>-0.323924492573525</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.3677476951103245</v>
+        <v>-0.222958388129598</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.3041305811963184</v>
+        <v>-0.1599600377421382</v>
       </c>
     </row>
     <row r="24">
@@ -3125,98 +3125,98 @@
         <v>3093</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.3110910845164696</v>
+        <v>-0.2660046243703533</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.2737801194011951</v>
+        <v>-0.2173199177947822</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.7333109663146331</v>
+        <v>-0.6905810179052025</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.088023886083469</v>
+        <v>-1.060439560439562</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.335465469729833</v>
+        <v>-1.273808745589122</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.8117060409052215</v>
+        <v>-0.774705735661243</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.4438047759595847</v>
+        <v>-0.382726842668788</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.3290289118894805</v>
+        <v>-0.2666003402005259</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.1313802368044108</v>
+        <v>-0.04492438806995125</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.1500820337124438</v>
+        <v>0.2628344866598482</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.1839955712388317</v>
+        <v>-0.07063024150993868</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.01204293689870894</v>
+        <v>0.1491918466470636</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.1737475888054192</v>
+        <v>0.3359931829348497</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.3911378509232861</v>
+        <v>0.5527069747917963</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; -0.1228</t>
+          <t>X &gt; -0.1227</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.01718323201458816</v>
+        <v>0.01445611818316195</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.03445562381195089</v>
+        <v>0.008406005211405443</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.5989308432986391</v>
+        <v>-0.5704450061907025</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.7739694338933063</v>
+        <v>-0.7614847838728451</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.210626741231422</v>
+        <v>-1.164681784318056</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.6757356854696255</v>
+        <v>-0.654366574287728</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.08204335118152528</v>
+        <v>-0.03636640290918081</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.2309632093314065</v>
+        <v>0.2782555364020709</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.4413337437732636</v>
+        <v>0.5127454315068789</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.6766902412419427</v>
+        <v>0.7747668676583004</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.2684091014562426</v>
+        <v>0.3670295419410152</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.6759265871598927</v>
+        <v>0.7984572226381061</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.7984128174632872</v>
+        <v>0.9462243045574894</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.014212847161552</v>
+        <v>1.161336353542652</v>
       </c>
     </row>
     <row r="26">
@@ -3229,358 +3229,358 @@
         <v>2769</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.4859766310359674</v>
+        <v>0.5371294300715519</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.6801090491298467</v>
+        <v>0.7407659240119955</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.5019250662602346</v>
+        <v>0.5472567537536079</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.2710369926561</v>
+        <v>0.2998968540484768</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.3396124636583906</v>
+        <v>-0.2779557395176795</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.03005771529959134</v>
+        <v>0.0670580205435698</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.7037205310717383</v>
+        <v>0.764798464362535</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.175504268440477</v>
+        <v>1.237932840129432</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.36730322660631</v>
+        <v>1.45375907534077</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.6728299014556</v>
+        <v>1.785582354403005</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.215277732789872</v>
+        <v>1.328643062518765</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.466345613862281</v>
+        <v>1.603494523610635</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.551688691613663</v>
+        <v>1.713934285743093</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.548611179541815</v>
+        <v>1.710180303410326</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; -0.09821</t>
+          <t>X &gt; -0.09819</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>2594</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.667702774624253</v>
+        <v>0.7051365386093522</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.446260233363937</v>
+        <v>1.492227268693682</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.8586390209847679</v>
+        <v>0.8886956449950603</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.8732406501227175</v>
+        <v>0.8857253001431786</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.2577184327375193</v>
+        <v>0.3193751568782304</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.6322613727662088</v>
+        <v>0.6692616780101872</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.434189182093782</v>
+        <v>1.495267115384578</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.738015806442583</v>
+        <v>1.800444378131537</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.75411692257331</v>
+        <v>1.84057277130777</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.983405769927806</v>
+        <v>2.096158222875211</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.393147434045069</v>
+        <v>1.506512763773962</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.620283097173079</v>
+        <v>1.757432006921434</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.701185001262871</v>
+        <v>1.863430595392302</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.603951823130522</v>
+        <v>1.765520946999033</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; -0.08593</t>
+          <t>X &gt; -0.08591</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>2441</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.9682577060087851</v>
+        <v>1.008709779041006</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.814693105744247</v>
+        <v>1.862503148901084</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.419824399147657</v>
+        <v>1.450729039398396</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.509110714876826</v>
+        <v>1.521595364897287</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.9706894998046565</v>
+        <v>1.032346223945368</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.268131437520317</v>
+        <v>1.305131742764296</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.043700874692938</v>
+        <v>2.104778807983735</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.395853813478013</v>
+        <v>2.458282385166967</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.498721194809015</v>
+        <v>2.585177043543474</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>2.877600516130954</v>
+        <v>2.990352969078359</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.140278572395104</v>
+        <v>2.253643902123997</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>2.420462631010494</v>
+        <v>2.557611540758849</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.450843005727208</v>
+        <v>2.613088599856638</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>2.413796619855205</v>
+        <v>2.575365743723715</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; -0.07366</t>
+          <t>X &gt; -0.07364</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>2247</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.667665373603995</v>
+        <v>1.712110397335245</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.592807381467509</v>
+        <v>2.643038346515638</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.286946240513998</v>
+        <v>2.319022923706513</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.239184241835346</v>
+        <v>2.251668891855807</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.433740329833931</v>
+        <v>1.495397053974642</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.998204964478838</v>
+        <v>2.035205269722816</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.84805068645889</v>
+        <v>2.909128619749687</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.226439161286642</v>
+        <v>3.288867732975596</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>3.343454406390499</v>
+        <v>3.429910255124959</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.739435140365686</v>
+        <v>3.85218759331309</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.089643987832723</v>
+        <v>3.203009317561616</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.613568756215088</v>
+        <v>3.750717665963442</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3.638351973485584</v>
+        <v>3.800597567615014</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.621050608832633</v>
+        <v>3.782619732701143</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; -0.06138</t>
+          <t>X &gt; -0.06137</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2035</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.806315979544323</v>
+        <v>1.834512622830246</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.258624430462127</v>
+        <v>2.291779852236139</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.962035822145637</v>
+        <v>1.974889563558918</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.797448659912845</v>
+        <v>1.809933309933307</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.160747346560576</v>
+        <v>1.222404070701288</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.654749480836436</v>
+        <v>1.691749786080415</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>2.945937139485537</v>
+        <v>3.007015072776333</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>3.314134576084861</v>
+        <v>3.376563147773815</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3.646255083022957</v>
+        <v>3.732710931757417</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>3.97549107735621</v>
+        <v>4.088243530303615</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.574177556478439</v>
+        <v>3.687542886207332</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.247381352644503</v>
+        <v>4.384530262392857</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>4.269387183960049</v>
+        <v>4.43163277808948</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>4.125988123115945</v>
+        <v>4.287557246984456</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; -0.0491</t>
+          <t>X &gt; -0.04909</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1783</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.07750952050791</v>
+        <v>2.086300731166823</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.372834393241916</v>
+        <v>2.384557416373312</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.202306684962778</v>
+        <v>2.215160426376059</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.220389318411549</v>
+        <v>2.23287396843201</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>2.130650099974261</v>
+        <v>2.192306824114972</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.82068878474545</v>
+        <v>2.857689089989428</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.857660059060386</v>
+        <v>3.918737992351183</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>4.287840653548663</v>
+        <v>4.350269225237618</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>4.675522764001236</v>
+        <v>4.761978612735696</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>4.722761572243087</v>
+        <v>4.835514025190491</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>4.125411500869973</v>
+        <v>4.238776830598866</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4.664561904429654</v>
+        <v>4.801710814178008</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>4.805159789278356</v>
+        <v>4.967405383407787</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>4.325772877022956</v>
+        <v>4.487342000891466</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; -0.03683</t>
+          <t>X &gt; -0.03682</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1509</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.443606080055105</v>
+        <v>2.426932575378096</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.422489723552076</v>
+        <v>2.434212746683471</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.093890069308038</v>
+        <v>2.106743810721319</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.02533604485788</v>
+        <v>2.037820694878341</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>2.017067248606132</v>
+        <v>2.078723972746843</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>2.314509186321793</v>
+        <v>2.351509491565771</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>3.555156516100531</v>
+        <v>3.616234449391328</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>3.750663640844543</v>
+        <v>3.813092212533498</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.418623330540306</v>
+        <v>4.505079179274766</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>4.695072035505753</v>
+        <v>4.807824488453157</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>3.960166292367767</v>
+        <v>4.07353162209666</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>4.789778077943815</v>
+        <v>4.92692698769217</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>4.965944938171873</v>
+        <v>5.128190532301304</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>5.21566627044816</v>
+        <v>5.377235394316671</v>
       </c>
     </row>
     <row r="33">
@@ -3590,101 +3590,101 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.856188854603609</v>
+        <v>1.801662636141209</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.978666608665037</v>
+        <v>3.037722698580716</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.832348026343517</v>
+        <v>2.892740929171488</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2.631200993250921</v>
+        <v>2.690950011845523</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>2.258479861028796</v>
+        <v>2.367538350163919</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2.63877184016949</v>
+        <v>2.723242608618008</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>3.962488827122556</v>
+        <v>4.072205093190227</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>3.992405676891174</v>
+        <v>4.103884770617832</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>5.174156412084187</v>
+        <v>5.310693256008392</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>5.732481931281612</v>
+        <v>5.896483248991089</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>4.782078234138851</v>
+        <v>4.946074144738589</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>6.142062054284608</v>
+        <v>6.330940716265999</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>6.550307857589907</v>
+        <v>6.764970186053745</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>6.965729272716246</v>
+        <v>7.179852527339435</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; -0.01228</t>
+          <t>X &gt; -0.01227</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>875</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.135133108361451</v>
+        <v>2.118459603684443</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>4.637845209682908</v>
+        <v>4.649568232814303</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.128690788800611</v>
+        <v>4.141544530213892</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4.144658207122397</v>
+        <v>4.157142857142858</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>3.606236992050228</v>
+        <v>3.667893716190939</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>4.246536072623023</v>
+        <v>4.283536377867001</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>5.761802355350746</v>
+        <v>5.822880288641542</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>6.208904670854963</v>
+        <v>6.271333242543918</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>7.2907619275298</v>
+        <v>7.37721777626426</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>8.154922456787588</v>
+        <v>8.267674909734993</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>6.80731198961287</v>
+        <v>6.920677319341763</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>8.44169514695831</v>
+        <v>8.578844056706664</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>8.364297678870535</v>
+        <v>8.526543272999966</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>8.499733296861109</v>
+        <v>8.661302420729619</v>
       </c>
     </row>
     <row r="35">
@@ -3759,7 +3759,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Drawdown-30 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Drawdown-30 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3848,53 +3848,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.356</t>
+          <t>X &lt; -0.3559</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2.268466441694791</v>
+        <v>2.251792937017782</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.656892828730534</v>
+        <v>0.6686158518619294</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>8.595357455467273</v>
+        <v>8.608211196880553</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.916086778550969</v>
+        <v>9.928571428571431</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10.56814175395499</v>
+        <v>10.6297984780957</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3.722726548813505</v>
+        <v>3.759726854057483</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9.590373783922182</v>
+        <v>9.651451717212979</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>5.551761813712098</v>
+        <v>5.614190385401052</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>5.490761927529796</v>
+        <v>5.577217776264256</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>9.402541504406642</v>
+        <v>9.515293957354046</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>11.57874056104144</v>
+        <v>11.69210589077034</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>16.37502848029163</v>
+        <v>16.51217739003999</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>11.19286910744197</v>
+        <v>11.3551147015714</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>12.63306663019445</v>
+        <v>12.79463575406296</v>
       </c>
     </row>
     <row r="7">
@@ -3907,202 +3907,202 @@
         <v>104</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1.352715525943871</v>
+        <v>1.336042021266863</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.2588580870203856</v>
+        <v>-0.2471350638889902</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>6.077042437152251</v>
+        <v>6.089896178565532</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.168834031298218</v>
+        <v>7.181318681318679</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.668874354687581</v>
+        <v>5.730531078828292</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.1970855231724826</v>
+        <v>0.2340858284164611</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.920044113592503</v>
+        <v>4.9811220468833</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.3548315928812968</v>
+        <v>-0.2924030211923423</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.5457069824748615</v>
+        <v>0.632162831209321</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.464812566677701</v>
+        <v>5.577565019625105</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>6.221597703898581</v>
+        <v>6.334963033627474</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>10.10213470739785</v>
+        <v>10.23928361714621</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>5.835726250299111</v>
+        <v>5.997971844428541</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>6.085447582575398</v>
+        <v>6.247016706443908</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.3315</t>
+          <t>X &lt; -0.3314</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.09276857634174718</v>
+        <v>-0.3733596881348404</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.380874002139748</v>
+        <v>-2.811237627991559</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.534602118849861</v>
+        <v>1.068528657198016</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>3.388993182491852</v>
+        <v>2.907814407814399</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.126434036385191</v>
+        <v>0.7091635574607764</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-3.748537819002593</v>
+        <v>-4.146256051925427</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.339142256828573</v>
+        <v>0.9212929870542439</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.438385969539127</v>
+        <v>-3.818044046833379</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-2.63731689020419</v>
+        <v>-3.000315801269309</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.684971717871335</v>
+        <v>1.304060746120825</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>3.20435632458824</v>
+        <v>2.809322007986452</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>6.687015344002631</v>
+        <v>6.286292164154759</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>2.818484870988769</v>
+        <v>2.472330818787519</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>3.068206203265056</v>
+        <v>2.721375680802886</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.3192</t>
+          <t>X &lt; -0.3191</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>121</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.4273226177306313</v>
+        <v>-0.4439961224076399</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3.691788792678366</v>
+        <v>-3.680065769546971</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.04557390568371744</v>
+        <v>0.05842764709699821</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.828719600274695</v>
+        <v>1.841204250295156</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.3625941767809522</v>
+        <v>-0.3009374526402411</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-5.023829925015697</v>
+        <v>-4.986829619771719</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1498859563375703</v>
+        <v>-0.0888080230467736</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-4.749300760077745</v>
+        <v>-4.68687218838879</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-3.983854365268314</v>
+        <v>-3.897398516533855</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.1246981356541781</v>
+        <v>0.2374505886015825</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1.572837373320063</v>
+        <v>1.686202703048956</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>5.739451935624182</v>
+        <v>5.876600845372536</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.013412200712338</v>
+        <v>2.175657794841769</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2.263133532988626</v>
+        <v>2.424702656857136</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.3069</t>
+          <t>X &lt; -0.3068</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>133</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.8900203264065709</v>
+        <v>0.8733468217295624</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.7215532865576861</v>
+        <v>-0.7098302634262907</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.642976503086317</v>
+        <v>2.655830244499597</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.525109334941945</v>
+        <v>3.537593984962406</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.7310490221254042</v>
+        <v>0.7927057462661153</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-2.730907536399528</v>
+        <v>-2.693907231155549</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.9437572425687861</v>
+        <v>1.004835175859583</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-3.282824652453307</v>
+        <v>-3.220396080764353</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-2.591944839387494</v>
+        <v>-2.505488990653035</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.069208171073299</v>
+        <v>1.181960624020704</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.368214245251963</v>
+        <v>2.481579574980856</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.658236500341758</v>
+        <v>4.795385410090113</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.982342791652492</v>
+        <v>2.144588385781923</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.983943823176901</v>
+        <v>3.145512947045411</v>
       </c>
     </row>
     <row r="11">
@@ -4115,46 +4115,46 @@
         <v>143</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.052016225244564</v>
+        <v>2.035342720567556</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.2588580870203856</v>
+        <v>-0.2471350638889902</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.842776702886525</v>
+        <v>2.855630444299806</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>3.672330534794717</v>
+        <v>3.684815184815179</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.036007221820455</v>
+        <v>1.097663945961166</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-2.862355036268085</v>
+        <v>-2.825354731024106</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.5494147429631298</v>
+        <v>0.6104926762539264</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.714971453021164</v>
+        <v>-2.652542881332209</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.377369940602065</v>
+        <v>-1.290914091867606</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.5697076715728073</v>
+        <v>0.6824601245202118</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>3.162157144458021</v>
+        <v>3.275522474186914</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>5.294442399705552</v>
+        <v>5.431591309453907</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>2.77628569085855</v>
+        <v>2.938531284987981</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.725307722435531</v>
+        <v>3.886876846304041</v>
       </c>
     </row>
     <row r="12">
@@ -4167,150 +4167,150 @@
         <v>170</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>4.565385209201786</v>
+        <v>4.548711704524777</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.6008704197669488</v>
+        <v>0.6125934428983442</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.147178183758584</v>
+        <v>3.160031925171864</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.865666610483743</v>
+        <v>3.878151260504204</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.150774807176269</v>
+        <v>2.21243153131698</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.669430313931592</v>
+        <v>-1.632430008687614</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2.363483027619651</v>
+        <v>2.424560960910448</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.633112135867727</v>
+        <v>-1.570683564178772</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.07059386030291392</v>
+        <v>0.1570497090373735</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.3969392635102764</v>
+        <v>0.5096917164576809</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>3.721597703898581</v>
+        <v>3.834963033627474</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>4.932451449479309</v>
+        <v>5.069600359227664</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.159255662063821</v>
+        <v>2.321501256193251</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.997212288457753</v>
+        <v>3.158781412326263</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.2701</t>
+          <t>X &lt; -0.27</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>204</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>4.859502856260612</v>
+        <v>4.842829351583603</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.7969488511394971</v>
+        <v>0.8086718742708925</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>4.323648771993888</v>
+        <v>4.336502513407169</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3.963705826170013</v>
+        <v>3.976190476190474</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.954696375803721</v>
+        <v>2.016353099944432</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1988420786374832</v>
+        <v>-0.1618417733935047</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.6968163609529938</v>
+        <v>0.7578942942437905</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.2605631162598812</v>
+        <v>-0.1981345445709266</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.3215630024421827</v>
+        <v>-0.2351071537077232</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2989000478240058</v>
+        <v>0.4116525007714102</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>2.545127115663291</v>
+        <v>2.658492445392184</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>4.050098508302831</v>
+        <v>4.187247418051186</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2.649451740495188</v>
+        <v>2.811697334624618</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.899173072771475</v>
+        <v>3.060742196639985</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.2578</t>
+          <t>X &lt; -0.2577</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>4.286222696739181</v>
+        <v>4.029972563298671</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.9797338295376292</v>
+        <v>1.180972693332691</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4.822153258534257</v>
+        <v>5.006643987718405</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>4.528677577582435</v>
+        <v>4.714587100663046</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.295341108272986</v>
+        <v>2.537574246630953</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.321596605310674</v>
+        <v>1.544536980639762</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.931778142275689</v>
+        <v>3.171644604494475</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.617137116375545</v>
+        <v>1.861929987571045</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.132408416633922</v>
+        <v>1.403016450164202</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.977198485843282</v>
+        <v>2.266951582429385</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>3.891089229322304</v>
+        <v>4.1725157762435</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>4.772930013786386</v>
+        <v>5.074564370148479</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>3.92894658928217</v>
+        <v>4.257465515314621</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>4.602396735117772</v>
+        <v>4.928451305600021</v>
       </c>
     </row>
     <row r="15">
@@ -4323,46 +4323,46 @@
         <v>285</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>3.646912556983004</v>
+        <v>3.630239052305996</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.9827073650713842</v>
+        <v>0.9944303882027796</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.447487781281801</v>
+        <v>4.460341522695082</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>5.279495299854219</v>
+        <v>5.29197994987468</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.039319698817131</v>
+        <v>4.100976422957842</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.231498478638059</v>
+        <v>2.268498783882038</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>3.901150726278068</v>
+        <v>3.962228659568865</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>3.083090134514116</v>
+        <v>3.14551870620307</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.671213055349355</v>
+        <v>2.757668904083815</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>2.522842256286339</v>
+        <v>2.635594709233743</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>4.072474896881033</v>
+        <v>4.185840226609926</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>4.808612440191382</v>
+        <v>4.945761349939737</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>4.037480636264021</v>
+        <v>4.199726230393452</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>4.638079161522768</v>
+        <v>4.799648285391278</v>
       </c>
     </row>
     <row r="16">
@@ -4372,153 +4372,153 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>4.563618736847083</v>
+        <v>4.546945232170074</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2.351444523282225</v>
+        <v>2.363167546413621</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>4.959578819688637</v>
+        <v>4.972432561101918</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5.690432552896738</v>
+        <v>5.702917202917199</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>5.152011337824568</v>
+        <v>5.213668061965279</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.647651473738421</v>
+        <v>3.684651778982399</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>5.36471955826795</v>
+        <v>5.425797491558747</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>4.597235859186149</v>
+        <v>4.659664430875104</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>4.836536273304148</v>
+        <v>4.922992122038607</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>4.286711388576528</v>
+        <v>4.399463841523932</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>6.484360466661343</v>
+        <v>6.597725796390236</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>6.218443323706474</v>
+        <v>6.355592233454828</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>6.398789313362172</v>
+        <v>6.561034907491603</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>6.236049992213957</v>
+        <v>6.20947916890637</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.221</t>
+          <t>X &lt; -0.2209</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.776484558967404</v>
+        <v>2.759811054290395</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.450257989704951</v>
+        <v>2.461981012836347</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5.65436100547339</v>
+        <v>5.667214746886671</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>7.327030590523052</v>
+        <v>7.339515240543513</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>6.531539966710518</v>
+        <v>6.593196690851229</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4.258287817022591</v>
+        <v>4.29528812226657</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>4.687692917231026</v>
+        <v>4.748770850521822</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>3.963440109709161</v>
+        <v>4.025868681398116</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>4.673648449747951</v>
+        <v>4.76010429848241</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>4.594731490941093</v>
+        <v>4.707483943888498</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>5.675325210325319</v>
+        <v>5.788690540054212</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>6.995055411372547</v>
+        <v>7.132204321120902</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>6.831870209168002</v>
+        <v>6.994115803297433</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>6.729777479482614</v>
+        <v>6.729021847832087</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.2087</t>
+          <t>X &lt; -0.2086</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.572640974944207</v>
+        <v>2.555967470267198</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.9610673619799499</v>
+        <v>0.9727903851113453</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>4.090427730273234</v>
+        <v>4.103281471686515</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>5.322002448783813</v>
+        <v>5.334487098804274</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>5.22410986807288</v>
+        <v>5.285766592213591</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3.759437268343603</v>
+        <v>3.796437573587582</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.894967868251946</v>
+        <v>3.956045801542743</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.64804878665106</v>
+        <v>3.710477358340015</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3.80731321764938</v>
+        <v>3.89376906638384</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.397716666982674</v>
+        <v>3.510469119930079</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>4.955077880110032</v>
+        <v>5.068443209838925</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>6.007636490383078</v>
+        <v>6.00766721592629</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>6.61006253348495</v>
+        <v>6.493566558084929</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>6.778352238894691</v>
+        <v>6.522347102919682</v>
       </c>
     </row>
     <row r="19">
@@ -4528,49 +4528,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.666036351459823</v>
+        <v>2.733333867996912</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.8668454777075638</v>
+        <v>0.9628908652380659</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3.47385294371886</v>
+        <v>3.378141640968295</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3.416488815538365</v>
+        <v>3.508025682182975</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>4.754240208346118</v>
+        <v>4.704169799658033</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3.925978581333823</v>
+        <v>4.040625730461976</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>4.216479385637527</v>
+        <v>4.354501476442508</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>4.124530508432017</v>
+        <v>4.263200551265157</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.875913361461727</v>
+        <v>4.038962024525361</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>4.526726262737739</v>
+        <v>4.713260784534356</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>5.447676503148109</v>
+        <v>5.561041832877002</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>6.913875598086115</v>
+        <v>6.932529395757847</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>7.365858077041104</v>
+        <v>7.287840512345987</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>7.359032488235769</v>
+        <v>7.161650852785371</v>
       </c>
     </row>
     <row r="20">
@@ -4580,101 +4580,101 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.847397692651761</v>
+        <v>1.630015563648044</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.07505237550743971</v>
+        <v>-0.1123971902976066</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.091759231611817</v>
+        <v>1.882399853234816</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.865099180939573</v>
+        <v>2.808462238398548</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.934395007668044</v>
+        <v>3.752334116554898</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.843499495673413</v>
+        <v>3.865883966584022</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.114643395148313</v>
+        <v>3.168285202199328</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>3.93570476287244</v>
+        <v>4.070558578611362</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.874704876690139</v>
+        <v>3.968363371882702</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>4.634885649794263</v>
+        <v>4.679103481163573</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>5.33450092970503</v>
+        <v>5.373424572089014</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>6.599276499370021</v>
+        <v>6.493450798279689</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>6.766146962273218</v>
+        <v>6.520479883013756</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>6.956598311910888</v>
+        <v>6.608753040849059</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.1719</t>
+          <t>X &lt; -0.1718</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.8398950131233605</v>
+        <v>0.6455683995169395</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.9800119331742323</v>
+        <v>-1.218113594474815</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.5499059889631752</v>
+        <v>0.3516827790618109</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.675891696250616</v>
+        <v>1.60358645562011</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>3.06915925497249</v>
+        <v>2.797366767683613</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.450734156992297</v>
+        <v>2.308415992634259</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.93804038265867</v>
+        <v>1.76517484359433</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.469430450353642</v>
+        <v>2.364693403509712</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.40843056417134</v>
+        <v>2.267727548579394</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.127492255034994</v>
+        <v>2.937408565909323</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>3.86445484675572</v>
+        <v>3.665231774787308</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>4.557125353375632</v>
+        <v>4.233073113768569</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.367244874940944</v>
+        <v>3.923503759322159</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4.274113292761918</v>
+        <v>3.832243979171182</v>
       </c>
     </row>
     <row r="22">
@@ -4684,49 +4684,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>798</v>
+        <v>807</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.59072009563161</v>
+        <v>1.411456802563997</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.5734134201630852</v>
+        <v>-0.784465380631076</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.579523826730416</v>
+        <v>1.39532604281893</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.145900443147241</v>
+        <v>2.995798319327726</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3.922797048908791</v>
+        <v>3.6094903548464</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3.421771795803956</v>
+        <v>3.217804563668935</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.910644535614374</v>
+        <v>2.613894679655935</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3.066902533341597</v>
+        <v>2.833484006908705</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.507149529952315</v>
+        <v>2.252094623554903</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.7792188586401</v>
+        <v>2.485465996576643</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.397003446720056</v>
+        <v>3.094222292886727</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3.130980861244012</v>
+        <v>2.731201464441071</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3.035350780962439</v>
+        <v>2.532625309775071</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.60800397355284</v>
+        <v>2.111328974101902</v>
       </c>
     </row>
     <row r="23">
@@ -4736,49 +4736,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>925</v>
+        <v>936</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.615419737420766</v>
+        <v>1.458142143366985</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.5958427676804732</v>
+        <v>0.4040655873116634</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.756803852207796</v>
+        <v>1.597629186298541</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.981550223029394</v>
+        <v>3.843915343915334</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>4.36311955214822</v>
+        <v>4.095406943704155</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>3.222011241231236</v>
+        <v>3.053512164791947</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.340105255458163</v>
+        <v>2.099565639345983</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.256830938136069</v>
+        <v>2.012431210393473</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.873250406792472</v>
+        <v>1.611072338280351</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.407513568582139</v>
+        <v>1.060380076908253</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.557804600450304</v>
+        <v>2.194920435118419</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.332032641179289</v>
+        <v>1.888865378668271</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.083026466281837</v>
+        <v>1.555602580821279</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.855717852845672</v>
+        <v>1.332486791913986</v>
       </c>
     </row>
     <row r="24">
@@ -4788,101 +4788,101 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1056</v>
+        <v>1068</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.014513036197883</v>
+        <v>0.8789318148530327</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.044800800908163</v>
+        <v>0.8742134112199267</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.201150288064227</v>
+        <v>2.058934104427976</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3.322680185144364</v>
+        <v>3.210173763098553</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>4.059087427999252</v>
+        <v>3.835130750280335</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.720220283149345</v>
+        <v>2.582527349720429</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.842759215987755</v>
+        <v>1.644807198940548</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.522975157806805</v>
+        <v>1.32448567670194</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.13839892766444</v>
+        <v>0.8741156593690391</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.2471057451972953</v>
+        <v>-0.08403084719464005</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.134251150546355</v>
+        <v>0.7910788132726623</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.6557918253271851</v>
+        <v>0.2482699579082563</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.1947612550294835</v>
+        <v>-0.2812610835415299</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.4486433265155085</v>
+        <v>-0.9159046418707035</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; -0.1228</t>
+          <t>X &lt; -0.1227</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1201</v>
+        <v>1214</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.1424760125742068</v>
+        <v>0.06552186276632455</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.3055404163723523</v>
+        <v>0.1994339027126841</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.523221670460202</v>
+        <v>1.441018890685797</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2.030042187304055</v>
+        <v>1.979733675972426</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.108480203384346</v>
+        <v>2.96227521367954</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.965075597614167</v>
+        <v>1.891205304684867</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.6854542001946484</v>
+        <v>0.5663926321538924</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.06724635293483061</v>
+        <v>-0.1820625419994073</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.4142368879167719</v>
+        <v>-0.5841557148877357</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.052902083817031</v>
+        <v>-1.28109356317141</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.132222894108061</v>
+        <v>-0.3721035234801704</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.048674167849917</v>
+        <v>-1.337133386902366</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.339814515091909</v>
+        <v>-1.687213340756642</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.876667321671064</v>
+        <v>-2.216739471480309</v>
       </c>
     </row>
     <row r="26">
@@ -4892,361 +4892,361 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1380</v>
+        <v>1392</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.8782193683076116</v>
+        <v>-0.9754936949797752</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.159609634323658</v>
+        <v>-1.273874206259826</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.9412896980023078</v>
+        <v>-1.025213907636626</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.4127929747892267</v>
+        <v>-0.4670643417966787</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.8154933943951761</v>
+        <v>0.6853710283149255</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.2164825526559611</v>
+        <v>0.1406792350098627</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.9822907541352919</v>
+        <v>-1.096020967357639</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.915770653820367</v>
+        <v>-2.024272725165055</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.154931728994178</v>
+        <v>-2.309580464864688</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.822203885078636</v>
+        <v>-3.023933768120102</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.976160792124553</v>
+        <v>-2.186542342716614</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.40899743108595</v>
+        <v>-2.663541678075063</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.573035516536514</v>
+        <v>-2.876758952412807</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.573972707279673</v>
+        <v>-2.876546511946898</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; -0.09821</t>
+          <t>X &lt; -0.09819</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1555</v>
+        <v>1567</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.026601585516097</v>
+        <v>-1.083352154626994</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.222433758317827</v>
+        <v>-2.286059994380189</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.370889579745281</v>
+        <v>-1.411567164686012</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.334483737195271</v>
+        <v>-1.345094664371771</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.3044681595756416</v>
+        <v>-0.4047676326125469</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.8038249547053766</v>
+        <v>-0.8593207649901373</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-2.006480066452795</v>
+        <v>-2.092966507510205</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-2.503971690451898</v>
+        <v>-2.588970090486683</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.403010966243087</v>
+        <v>-2.528925444382779</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.834393038493268</v>
+        <v>-3.000998364794427</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.913832334612337</v>
+        <v>-2.088603845353418</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.229889402082897</v>
+        <v>-2.442115608230068</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.35836115329986</v>
+        <v>-2.611722033122476</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.202333767906914</v>
+        <v>-2.455918839184676</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; -0.08593</t>
+          <t>X &lt; -0.08591</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1708</v>
+        <v>1720</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.302270394585335</v>
+        <v>-1.354042460725132</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.418965421546332</v>
+        <v>-2.474791800216245</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.969339627554419</v>
+        <v>-2.001477765409568</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-2.041338799363558</v>
+        <v>-2.045004128819166</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.267978832893611</v>
+        <v>-1.347259551593915</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.5803037542168</v>
+        <v>-1.622217590386967</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-2.567060618410189</v>
+        <v>-2.636578723683712</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-3.06217384223055</v>
+        <v>-3.130222791225336</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-3.092759046534077</v>
+        <v>-3.195038952514203</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-3.678789158699722</v>
+        <v>-3.814724825100939</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.684013050046481</v>
+        <v>-2.827834412687089</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-3.027644869750134</v>
+        <v>-3.20326976443156</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-3.065678079718445</v>
+        <v>-3.277158893514518</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-3.018767874099069</v>
+        <v>-3.229727479602609</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; -0.07366</t>
+          <t>X &lt; -0.07364</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1902</v>
+        <v>1914</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-1.892916126998493</v>
+        <v>-1.938386253161418</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.903340041847173</v>
+        <v>-2.949837766591692</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-2.64415664604369</v>
+        <v>-2.667900079230726</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-2.539083574108929</v>
+        <v>-2.538016038016046</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.585181113653597</v>
+        <v>-1.648264072977781</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-2.149873800226644</v>
+        <v>-2.180266208724341</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-3.045261926621869</v>
+        <v>-3.098604057309231</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-3.485375053613446</v>
+        <v>-3.537595328884656</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-3.519276277579195</v>
+        <v>-3.59980894896465</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-4.027478982277017</v>
+        <v>-4.136079000588254</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-3.312523031009555</v>
+        <v>-3.42638281926768</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-3.880573760604726</v>
+        <v>-4.019187556773808</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-3.905471857951014</v>
+        <v>-4.073829722151089</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-3.890893111430913</v>
+        <v>-4.058625926784934</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; -0.06138</t>
+          <t>X &lt; -0.06137</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2114</v>
+        <v>2126</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.670683266143214</v>
+        <v>-1.691206817867794</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-2.035397634020889</v>
+        <v>-2.057725035452286</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-1.841057110359053</v>
+        <v>-1.843133589981306</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.638930708669918</v>
+        <v>-1.641787051899414</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.022038359541192</v>
+        <v>-1.075900194816093</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.406082750589576</v>
+        <v>-1.433962617982502</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-2.550125980339963</v>
+        <v>-2.594881415196106</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.898372957177386</v>
+        <v>-2.942496829822737</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-3.123476594684185</v>
+        <v>-3.189625422770398</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-3.476859547798952</v>
+        <v>-3.566530321653339</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-3.137164695723527</v>
+        <v>-3.229386426212827</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-3.739293240835387</v>
+        <v>-3.851231131263269</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-3.756472331261172</v>
+        <v>-3.89271926981688</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-3.62363472584466</v>
+        <v>-3.760038796848661</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; -0.0491</t>
+          <t>X &lt; -0.04909</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2366</v>
+        <v>2378</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-1.505628316006529</v>
+        <v>-1.50592772446857</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-1.665987542930331</v>
+        <v>-1.66651066736501</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-1.618096878727492</v>
+        <v>-1.619718401078345</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.591849729385544</v>
+        <v>-1.593323761665481</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.518575038024963</v>
+        <v>-1.557745161060843</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.956857837594818</v>
+        <v>-1.975115280617004</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-2.651514121682538</v>
+        <v>-2.684577033910116</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-2.970281067521341</v>
+        <v>-3.002779892643048</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-3.177973386081092</v>
+        <v>-3.227709985860315</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-3.246644752374557</v>
+        <v>-3.316060246796127</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-2.838132139917377</v>
+        <v>-2.910102065070546</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-3.203478598215447</v>
+        <v>-3.291744178587464</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-3.305591873908746</v>
+        <v>-3.412494738169194</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-2.948787413198062</v>
+        <v>-3.057020299443394</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; -0.03683</t>
+          <t>X &lt; -0.03682</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2640</v>
+        <v>2652</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.34379640539656</v>
+        <v>-1.328123081922627</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-1.276957634531698</v>
+        <v>-1.27797359472752</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.161517757839476</v>
+        <v>-1.163707333956488</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-1.086608639238797</v>
+        <v>-1.088923473220994</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-1.076414143149037</v>
+        <v>-1.10719620703879</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.174050893281162</v>
+        <v>-1.190147832659306</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.805276278142699</v>
+        <v>-1.832457378580287</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.912334936098937</v>
+        <v>-1.939824448523488</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-2.21785270925119</v>
+        <v>-2.257880884954083</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-2.404965159378392</v>
+        <v>-2.459390494740042</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-2.021875621867586</v>
+        <v>-2.078407964489287</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-2.459007783721923</v>
+        <v>-2.527367591479369</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-2.555981436183288</v>
+        <v>-2.638477458247678</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-2.702431205303391</v>
+        <v>-2.783903353887915</v>
       </c>
     </row>
     <row r="33">
@@ -5256,101 +5256,101 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2942</v>
+        <v>2955</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.7167885740170803</v>
+        <v>-0.6907048168007321</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-1.126000423357034</v>
+        <v>-1.144182068114965</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.13042584803361</v>
+        <v>-1.149198172801242</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-1.015968970577951</v>
+        <v>-1.035051794748256</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.8585739679149214</v>
+        <v>-0.8990235770421506</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.9495898353672914</v>
+        <v>-0.9792764084017307</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.423044808336705</v>
+        <v>-1.460731170797061</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-1.431180616991519</v>
+        <v>-1.469565102609749</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-1.847208890250997</v>
+        <v>-1.89382469477821</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-2.102162210073047</v>
+        <v>-2.158936397173704</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-1.745295335150658</v>
+        <v>-1.803982199638241</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-2.2698343561473</v>
+        <v>-2.336156667966037</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-2.433896583543905</v>
+        <v>-2.510147235409079</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-2.60761835896097</v>
+        <v>-2.682763327397041</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; -0.01228</t>
+          <t>X &lt; -0.01227</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3274</v>
+        <v>3286</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.5311626889352539</v>
+        <v>-0.5246616884820057</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-1.153094708585073</v>
+        <v>-1.152112439454598</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-1.075223105524245</v>
+        <v>-1.074833995718777</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-1.050504486456859</v>
+        <v>-1.050104022191405</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.9025659321045154</v>
+        <v>-0.9161947295060031</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-1.01523810688424</v>
+        <v>-1.021693910969837</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.357943366772297</v>
+        <v>-1.369762112989626</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-1.473499510329709</v>
+        <v>-1.485271513574816</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-1.701108416216115</v>
+        <v>-1.718654082050627</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-1.955284115163948</v>
+        <v>-1.979133600903303</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-1.624755668087985</v>
+        <v>-1.649986799148451</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-2.031564926301776</v>
+        <v>-2.061858063557509</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-2.007785200082566</v>
+        <v>-2.045076527947487</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-2.046806540821059</v>
+        <v>-2.083780615528099</v>
       </c>
     </row>
     <row r="35">
@@ -5360,49 +5360,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3603</v>
+        <v>3615</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.3916684087055486</v>
+        <v>-0.3877303474889686</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.6057034961064574</v>
+        <v>-0.6055580029570891</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.6813969651720413</v>
+        <v>-0.6811802353680179</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.6192815342876017</v>
+        <v>-0.6192118226601053</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.4783698739519906</v>
+        <v>-0.4865685985362873</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.4981725557743317</v>
+        <v>-0.5023947762672947</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.5402158480524903</v>
+        <v>-0.5481223144980021</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.7430171119895164</v>
+        <v>-0.750468154071072</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.5672044962902874</v>
+        <v>-0.5790568882976999</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.8476994292276956</v>
+        <v>-0.8628031228706945</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.5934328008157905</v>
+        <v>-0.6094814108169686</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.8209955603926034</v>
+        <v>-0.8400745419741824</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.9761494433745881</v>
+        <v>-0.9987095715006689</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-1.12729180127139</v>
+        <v>-1.149248853722064</v>
       </c>
     </row>
   </sheetData>
